--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -26,6 +26,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCA" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MassArt" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="U Michigan Stamps" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UCLA" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columbia College Chicago" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$6</definedName>
@@ -47,6 +50,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'CCA'!$A$5:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'U Michigan Stamps'!$A$5:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24110,6 +24116,3557 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: CalArts 'High Pass' BFA Class of 2026 group exhibition page (names only; site requires crawl4ai due to cookie-consent/Cloudflare Turnstile blocking a plain fetch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rita Aldridge</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Adrian Anguiano</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Elyse Beavers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Raven Bridgewaters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jessica Yuexi Chen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Indie Courtney</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Xochitl Quetzalli Cruz</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sophie Darling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ivan Nuñez DelaCruz</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Angharad Fitzgerald</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Jonathan Jin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Amaris Jordan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Riley Kate</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sadira Kuelling</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mackenzie Lord</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Eugenia Moreeva</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ethan Nahman</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mike Nott</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Elizaveta Novikova</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Okey Ofomata</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Natalee Park</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Suzy Park</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Abraham Perez</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ella Rose</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Solomon Rosenthal</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Frances Sheehy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Elliot Smolin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Marisa del toro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QQ Yi</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BFA Art / Photo Media</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://calarts.edu/high-pass</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CalArts</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Name only, from 'High Pass' BFA Class of 2026 group exhibition page; no email/portfolio published on source page</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I34"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: UCLA Department of Art — current Graduate Students directory by area of study (Ceramics, Interdisciplinary Studio, New Genres, Painting and Drawing, Photography, Sculpture), each linking to a personal portfolio/Instagram where available</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://www.art.ucla.edu/graduate-students</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dane Nakama</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.bydanenakama.com/</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ethan Shaw</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/niceguysfinishinlast</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>g.aguilar magaña</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.geneaguilarstudio.com/</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lynsey Robertson</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.lynseyjrobertson.com/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Utē Petit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Victor Saucedo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Felix Li</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lucas Wrench</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.lucaswrench.info</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sabaah Folayan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.sabaah.is/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vanessa Norton</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.vanessanorton.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vincent hernandez</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MFA Interdisciplinary Studio</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carlos Camacho</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Emir West</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jazmin Jazzy Romero</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.jazminromero.com/</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Markele Cullins</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://markelecullins.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Samar Al Summary</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MFA New Genres</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.samaralsummary.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Anja Salonen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/anjasalonen/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dilan Torres</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Gillian N Haigh</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://gilliannhaigh.com/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jacqueline Valenzuela</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://jacquelinevalenzuela.com/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jerry Alexis Peña</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jerryalexispena</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Luke Francis Austin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/l.f.austin/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Magnus Maxine Flowers</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Roshini Agarwal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/roshini_agarwal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tammy Chang</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.tammy-chang.com/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Victor Ballesteros</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>http://instagram.com/vmballesterosg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Wihro Kim</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No portfolio/social link listed for this student</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alina van Ryzin</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alinavanryzin</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Andrés de Varona</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.andresmario.com/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Anne Vetter</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.acvetter.com/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ashley Michelle Hannah</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://ashleymichellehannah.com/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Keegan Isaac Holden</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.keeganholden.com/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>abhishek kulkarni</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.ar.kay/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Andrew Sungtaek</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.sungtaek</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aryana Polat</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://aryanapolat.com/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>libbi ponce</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://libbiponce.com/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tunmi da silva</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.tunmidasilva.com/</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Yao Wang</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MFA Sculpture</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://wangyao.info/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I43"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: Columbia College Chicago — 'Human Condition' 2026 BA/BFA Fine Art Exhibition page, Hokin Gallery and C33 Gallery exhibitor lists (names only). Note: 2 of 24 names have unusual letter-spacing in the source HTML itself (e.g. 'Faith H o g a n') — kept verbatim, flagged in notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jupiter Brodie</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Carley Brown</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fiona Connors</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jocelyn Diaz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Faith H o g a n</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Emelia Kay</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aja "Morningstar" Martin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hai Martinez</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Frida Mejia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nat Slavin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brianna Wilkins</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Isa Woodard</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Liz Z e r m e n o Robles</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (Hokin Gallery)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Name only, from 'Hokin Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jala Bowers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jenna Davis</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Trevell Hampton</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alivia King</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ana Lara</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Drew Malapanes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Elise N e a l</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published; NOTE: name appears to have unusual letter-spacing in the source HTML itself (e.g. single letters separated by spaces) — kept verbatim, may not reflect the person's actual name spelling</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wang Jing Yi (Eliana Pinkert)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cristian Romero</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Liza Smith</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Stefanie Valle Aguilera</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BFA/BA Fine Art (C33 Gallery)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Columbia College Chicago</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I29"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -29,6 +29,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UCLA" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columbia College Chicago" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iowa" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UW Art" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BGSU" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$6</definedName>
@@ -53,6 +56,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27667,6 +27673,1638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: University of Iowa School of Art, Art History, and Design — MFA Virtual Exhibitions page (2024-2026 cohorts), each linking to a Matterport 3D exhibition tour rather than a personal portfolio site</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://art.uiowa.edu/events/mfa-virtual-exhibitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Heather Steckler</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=bUQuRPrPXn5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cara Krippner</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=QMBBNq3N6VX</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Anna Roemerman</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA 3D Design</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=1RzXZaJURgK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Antonia Baafi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Jewelry and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=E4APuduuJ7R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lya Finston</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=PkmkecLPwnV</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Amanda Shepard</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Jewelry and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=uCPoUCvVax8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ben Eastman</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA 3D Design</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=1ncCV6yM24a</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Javier Espinosa Momox</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=gAnFZ1qj4mX</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Patrick Ryan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA Ceramics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=e6BTTHxyJVm</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Al-Qawi Nanavati</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=ZLZKMucHd3u</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gracie Baer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MFA Sculpture &amp; Intermedia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=59w5kkDgyys</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Braden Dexter</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MFA Graphic Design</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=c5LN5QkVjdo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Agnes Harry Mills</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MFA Jewlery and Metal Arts</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=vccXRs9sB2o</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kyle Agnew</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MFA Photography</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=3veaLSxJd3y</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sofia Echeverri</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=L2tVk5UcqYH</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Na'ah Gordon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=8mfrTxRfsF9</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jordan Ramsey Ismaiel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MFA Painting and Drawing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=Gt8PNGatZUC</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lauren Krukowski</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MFA Printmaking</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://my.matterport.com/show/?m=MbXETFgfm4h</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>University of Iowa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Portfolio URL is a Matterport 3D virtual exhibition tour, not a personal site; no email published on source page</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I23"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: University of Washington 2026 MFA + MDes Thesis Exhibition page (Henry Art Gallery) — names only; source does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stephanie Alacon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dahae Cheon</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Li-Yuan Chiou</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jeff Jiang</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Victoria Mackender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Alex Moni-Sauri</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Oscar Pearson</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chave Pichardo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andrew Roibal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ryan Walters</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I15"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: BGSU ScholarWorks — School of Art MA and MFA Graduate Exhibitions, Portfolios, and Theses repository, 2025 cohort (thesis title + author name; portfolio_url is the repository record, not a personal site)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://scholarworks.bgsu.edu/ms_art/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Syed Fatmi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/542</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Thesis title: "OMNISYS"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nick Felaris</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/543</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Precious Gyekye</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Peter Kiladejo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Thesis title: "Adetope Peter Kiladejo Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rachel Krieger</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kamrun Mim</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MFA Studio Art</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://scholarworks.bgsu.edu/ms_art/547</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BGSU</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Thesis title: "Kamrun Mim"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I11"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -58,7 +58,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28975,7 +28975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29060,7 +29060,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Syed Fatmi</t>
+          <t>Nick Felaris</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/542</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/543</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -29092,14 +29092,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Thesis title: "OMNISYS"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nick Felaris</t>
+          <t>Precious Gyekye</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/543</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -29131,14 +29131,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Precious Gyekye</t>
+          <t>Peter Kiladejo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -29170,14 +29170,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Adetope Peter Kiladejo Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Peter Kiladejo</t>
+          <t>Rachel Krieger</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -29193,7 +29193,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -29209,14 +29209,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Thesis title: "Adetope Peter Kiladejo Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rachel Krieger</t>
+          <t>Kamrun Mim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -29232,7 +29232,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
+          <t>https://kamrunnahermim.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -29248,56 +29248,17 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kamrun Mim</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/547</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BGSU</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Thesis title: "Kamrun Mim"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Kamrun Mim"; personal site found via web search (kamrunnahermim.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting contact page manually</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I11"/>
+  <autoFilter ref="A5:I10"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -58,7 +58,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28975,7 +28975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29060,7 +29060,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nick Felaris</t>
+          <t>Precious Gyekye</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -29076,7 +29076,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/543</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -29092,14 +29092,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Thesis title: "Nick Felaris Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
+          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Precious Gyekye</t>
+          <t>Peter Kiladejo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/544</t>
+          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -29131,134 +29131,17 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Thesis title: "Unraveling Silence"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Peter Kiladejo</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/545</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BGSU</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
           <t>Thesis title: "Adetope Peter Kiladejo Master of Fine Arts"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Rachel Krieger</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://scholarworks.bgsu.edu/ms_art/546</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BGSU</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Thesis title: "Rachel Krieger"; no email/personal portfolio published on source page (portfolio_url is the ScholarWorks repository record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Kamrun Mim</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://kamrunnahermim.com/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BGSU</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Thesis title: "Kamrun Mim"; personal site found via web search (kamrunnahermim.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting contact page manually</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I10"/>
+  <autoFilter ref="A5:I7"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -28701,7 +28701,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://jeff-jiang.com/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -28717,7 +28717,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (jeff-jiang.com, footwear/product design background) but no email visible in static HTML — likely a JS-rendered contact form; no email found</t>
         </is>
       </c>
     </row>
@@ -28740,7 +28740,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://www.vamack.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -28756,7 +28756,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (vamack.com) but this tool's fetcher could not resolve the domain (DNS failure) — try visiting manually for contact info; also has Instagram @vamackender</t>
         </is>
       </c>
     </row>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://oscarpearsonart.wixsite.com/studio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -28834,7 +28834,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (Wix site, Instagram @oscarpearson_) but no email visible — only a Wix contact form; no email found. NOTE: a different, unrelated Oscar Pearson (California muralist/gallery artist) also shows up in search — not to be confused with this student</t>
         </is>
       </c>
     </row>
@@ -28935,7 +28935,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://www.ryanwalters.art/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -28951,7 +28951,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (ryanwalters.art) but this tool's fetcher could not resolve the .art domain (DNS failure) — try visiting manually for contact info</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -51,7 +51,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'SVA'!$A$5:$I$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'MICA'!$A$5:$I$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'CCA'!$A$5:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'U Michigan Stamps'!$A$5:$I$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
@@ -17747,7 +17747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17871,7 +17871,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Olivia Greenberg</t>
+          <t>Lisa Spencer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://visura.co/lspencer/about</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -17903,20 +17903,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Photographer/writer based in Winchester, MA; Visura profile found via web search but returned HTTP 403 on fetch — no email found</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anastasia Sierra</t>
+          <t>Christopher Gage Arotsky</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Film/Video</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -17949,13 +17949,13 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lisa Spencer</t>
+          <t>Camryn Connolly</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Studio Arts</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://camrynconnolly.com/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -17981,20 +17981,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Personal site found via web search (camrynconnolly.com) but only a contact form is shown, no visible email; Instagram @camrynscollections</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shailee Thakkar</t>
+          <t>Suzi Grossman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Studio Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-mfa-thesis-exhibition-PARTI</t>
+          <t>https://www.suzigrossman.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -18020,20 +18020,20 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED possible email: Suzi@suzigrossman.com — surfaced via web search summary of the site's contact page, but the email is JS-obfuscated on the live page and could not be independently confirmed by direct fetch; not written as confirmed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Christopher Gage Arotsky</t>
+          <t>Robin Jamkatel</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Film/Video</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18066,13 +18066,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Antonio Bailey</t>
+          <t>Dylan Record</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Film/Video</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18102,169 +18102,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Camryn Connolly</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MFA Studio Arts</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Suzi Grossman</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MFA Photography</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Robin Jamkatel</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MFA Photography</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Dylan Record</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MFA Film/Video</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I16"/>
+  <autoFilter ref="A5:I12"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VCU'!$A$5:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Yale'!$A$5:$I$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UW-Madison'!$A$5:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ohio State'!$A$5:$I$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Pratt'!$A$5:$I$112</definedName>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No email found — Behance profile has no listed contact info, no personal site found</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -717,7 +721,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Own site returned HTTP 503 (site appears down) on repeated fetch attempts; CMU directory page has no direct email listed — try visiting waltersmits.com manually</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -748,108 +756,19 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Amber N. Ford</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MFA Studio Art (First-Year MFA)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://art.cmu.edu/people/amber-ford/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sarah Al-Sarraj</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MFA Studio Art (First-Year MFA)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https:\/\/www.sarahalsarraj.com\/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Stefanie Zito</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MFA Studio Art (First-Year MFA)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https:\/\/www.stefaniezito.com\/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Own site (yiyingwang666.com) could not be resolved by this tool's fetcher (DNS failure) — try visiting manually; CMU directory page has no direct email listed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I11"/>
+  <autoFilter ref="A5:I8"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RISD'!$A$5:$I$215</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Otis'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parsons'!$A$5:$I$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VCU'!$A$5:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Yale'!$A$5:$I$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$8</definedName>
@@ -39554,7 +39554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -39639,13 +39639,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Charles Jarboe</t>
+          <t>Natalia Purchiaroni</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -39667,14 +39667,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Natalia Purchiaroni</t>
+          <t>Macy West</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -39702,20 +39702,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Macy West</t>
+          <t>Mo (Maria-Fernanda) Nunez Alzate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Sculpture</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -39723,7 +39723,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://fernandanunez.com/</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39737,20 +39741,20 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: February 26 - March 1); no email/major/portfolio published on source page</t>
+          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch — try visiting manually</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amanda Crain-Freeland</t>
+          <t>Mika Obayashi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Fiber/Sculpture</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -39758,7 +39762,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.mikaobayashi.com/</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39772,20 +39780,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (mikaobayashi.com) but no email visible — only Instagram and a /contact link; no email found</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mo (Maria-Fernanda) Nunez Alzate</t>
+          <t>Heather Swenson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -39807,20 +39815,20 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mika Obayashi</t>
+          <t>Sophia Dell'Arciprete</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -39828,7 +39836,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://sophiadellarciprete.com/</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39842,20 +39854,20 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (sophiadellarciprete.com) but no email visible in static HTML; no email found</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Heather Swenson</t>
+          <t>Ari Zuaro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Ceramics</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -39863,7 +39875,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://arizuaro.com/</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39877,20 +39893,20 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 12-March 15); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (arizuaro.com) but no email visible — only Instagram link; no email found</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sophia Dell'Arciprete</t>
+          <t>Theodora Dagkli Andonopoulos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -39912,14 +39928,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced, only a LinkedIn profile</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rae Helms</t>
+          <t>Jess Lauro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -39947,14 +39963,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Francesca Lally</t>
+          <t>Esther Park</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -39982,14 +39998,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ari Zuaro</t>
+          <t>Mollie Hansen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -40017,20 +40033,20 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 19 - March 22); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lilly Buttitta</t>
+          <t>Maedeh Mehdipour</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Fiber and Material Studies</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -40038,7 +40054,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://maedehmehdipour.com/</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -40052,20 +40072,20 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (maedehmehdipour.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting manually</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Theodora Dagkli Andonopoulos</t>
+          <t>Ally Messer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Printmaking</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -40087,14 +40107,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — only a LinkedIn profile surfaced, no personal site</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jess Lauro</t>
+          <t>Madeline Rodriguez</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -40122,14 +40142,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Esther Park</t>
+          <t>Ruoxua Fan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -40157,14 +40177,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: March 26- March 29); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mollie Hansen</t>
+          <t>Ivy Jewell</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -40192,14 +40212,14 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maedeh Mehdipour</t>
+          <t>Angelique Scott</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -40227,14 +40247,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ally Messer</t>
+          <t>Ben Solo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -40248,7 +40268,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.bensoloart.com/</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -40262,14 +40286,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>Own site (bensoloart.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Madeline Rodriguez</t>
+          <t>Logan Crompton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -40283,7 +40307,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://scoby.page/log3y-logan-crompton</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -40297,14 +40325,14 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 2 - April 5); no email/major/portfolio published on source page</t>
+          <t>Link-in-bio page (scoby.page) found via web search — not fetched for email this pass</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ruoxua Fan</t>
+          <t>Boi Boy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -40332,20 +40360,20 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced (full name may be 'Boi Boy Cottrell' per one source)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ivy Jewell</t>
+          <t>Diego Juarez</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -40353,7 +40381,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.diegojuarez.com/</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -40367,20 +40399,20 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>Personal site found via web search (diegojuarez.com/bio) but no email visible — only Instagram link and a /contact link not checked; no email found</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Angelique Scott</t>
+          <t>Gianna Santucci</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -40402,20 +40434,20 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ben Solo</t>
+          <t>Dora Moghaddamikhomami</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -40437,20 +40469,20 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 9 - April 12); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Logan Crompton</t>
+          <t>Marissa Raybuck</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -40472,20 +40504,20 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced; works at Running Press Book Publishers</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Boi Boy</t>
+          <t>Pegah Saebi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Design</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -40493,7 +40525,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://pegahsaebi.com/</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -40507,192 +40543,17 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Diego Juarez</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Gianna Santucci</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Name only, from exhibition schedule text (week: April 16- April 19); no email/major/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dora Moghaddamikhomami</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Marissa Raybuck</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Pegah Saebi</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Name only, from exhibition schedule text (week: April 23 - April 26); no email/major/portfolio published on source page</t>
+          <t>Own site (pegahsaebi.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I35"/>
+  <autoFilter ref="A5:I30"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -40,10 +40,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RISD'!$A$5:$I$215</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Otis'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parsons'!$A$5:$I$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VCU'!$A$5:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Yale'!$A$5:$I$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UW-Madison'!$A$5:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ohio State'!$A$5:$I$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Pratt'!$A$5:$I$112</definedName>
@@ -51,13 +51,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'SVA'!$A$5:$I$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'MICA'!$A$5:$I$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'CCA'!$A$5:$I$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'MassArt'!$A$5:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'U Michigan Stamps'!$A$5:$I$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'CalArts'!$A$5:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'UCLA'!$A$5:$I$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Columbia College Chicago'!$A$5:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -692,83 +692,13 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Walter Smits</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MFA Studio Art (First-Year MFA)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https:\/\/waltersmits.com</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Own site returned HTTP 503 (site appears down) on repeated fetch attempts; CMU directory page has no direct email listed — try visiting waltersmits.com manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Yiying Wang</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MFA Studio Art (First-Year MFA)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https:\/\/yiyingwang666.com\/lander</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CMU</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Own site (yiyingwang666.com) could not be resolved by this tool's fetcher (DNS failure) — try visiting manually; CMU directory page has no direct email listed</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I8"/>
+  <autoFilter ref="A5:I6"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17666,7 +17596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -17790,13 +17720,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lisa Spencer</t>
+          <t>Christopher Gage Arotsky</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Film/Video</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17806,7 +17736,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://visura.co/lspencer/about</t>
+          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -17822,20 +17752,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Photographer/writer based in Winchester, MA; Visura profile found via web search but returned HTTP 403 on fetch — no email found</t>
+          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christopher Gage Arotsky</t>
+          <t>Camryn Connolly</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Film/Video</t>
+          <t>MFA Studio Arts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17845,7 +17775,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
+          <t>https://camrynconnolly.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -17861,20 +17791,20 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
+          <t>Personal site found via web search (camrynconnolly.com) but only a contact form is shown, no visible email; Instagram @camrynscollections</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Camryn Connolly</t>
+          <t>Robin Jamkatel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Studio Arts</t>
+          <t>MFA Photography</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17884,7 +17814,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://camrynconnolly.com/</t>
+          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -17900,20 +17830,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Personal site found via web search (camrynconnolly.com) but only a contact form is shown, no visible email; Instagram @camrynscollections</t>
+          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Suzi Grossman</t>
+          <t>Dylan Record</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Film/Video</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17923,7 +17853,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.suzigrossman.com/</t>
+          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -17939,95 +17869,17 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UNVERIFIED possible email: Suzi@suzigrossman.com — surfaced via web search summary of the site's contact page, but the email is JS-obfuscated on the live page and could not be independently confirmed by direct fetch; not written as confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Robin Jamkatel</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MFA Photography</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dylan Record</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MFA Film/Video</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://calendar.massart.edu/event/2026-spring-mfa-thesis-exhibition-part-ii</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MassArt</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Name only, from 'FEATURED ARTISTS' list; no email/portfolio published on source page</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I12"/>
+  <autoFilter ref="A5:I10"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -28246,7 +28098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -28409,7 +28261,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Li-Yuan Chiou</t>
+          <t>Jeff Jiang</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -28425,7 +28277,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
+          <t>https://jeff-jiang.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -28441,14 +28293,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
+          <t>Personal site found via web search (jeff-jiang.com, footwear/product design background) but no email visible in static HTML — likely a JS-rendered contact form; no email found</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jeff Jiang</t>
+          <t>Alex Moni-Sauri</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -28464,7 +28316,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jeff-jiang.com/</t>
+          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -28480,251 +28332,17 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Personal site found via web search (jeff-jiang.com, footwear/product design background) but no email visible in static HTML — likely a JS-rendered contact form; no email found</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Victoria Mackender</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://www.vamack.com/</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Personal site found via web search (vamack.com) but this tool's fetcher could not resolve the domain (DNS failure) — try visiting manually for contact info; also has Instagram @vamackender</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Alex Moni-Sauri</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
           <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Oscar Pearson</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://oscarpearsonart.wixsite.com/studio</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Personal site found via web search (Wix site, Instagram @oscarpearson_) but no email visible — only a Wix contact form; no email found. NOTE: a different, unrelated Oscar Pearson (California muralist/gallery artist) also shows up in search — not to be confused with this student</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chave Pichardo</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Andrew Roibal</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://henryart.org/exhibitions/2026-university-of-washington-mfa-mdes-thesis-exhibition</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Name only, from Henry Art Gallery thesis exhibition page; no email/portfolio published; source page does not map a specific discipline to each individual student</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ryan Walters</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MFA/MDes (UW Art — discipline not specified per student)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://www.ryanwalters.art/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>University of Washington</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Personal site found via web search (ryanwalters.art) but this tool's fetcher could not resolve the .art domain (DNS failure) — try visiting manually for contact info</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I15"/>
+  <autoFilter ref="A5:I9"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -39554,7 +39172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -39639,13 +39257,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Natalia Purchiaroni</t>
+          <t>Mo (Maria-Fernanda) Nunez Alzate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Sculpture</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -39653,7 +39271,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://fernandanunez.com/</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39667,20 +39289,20 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch; not resolved this pass — still needs manual check</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Macy West</t>
+          <t>Theodora Dagkli Andonopoulos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -39702,20 +39324,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>No email found via web search — no personal site surfaced</t>
+          <t>No email found via web search — no personal site surfaced, only a LinkedIn profile</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mo (Maria-Fernanda) Nunez Alzate</t>
+          <t>Jess Lauro</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Sculpture</t>
+          <t>MFA Fine Arts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -39723,11 +39345,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://fernandanunez.com/</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39741,20 +39359,20 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Own site (fernandanunez.com) found via web search but returned HTTP 503 on fetch — try visiting manually</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mika Obayashi</t>
+          <t>Ally Messer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Fiber/Sculpture</t>
+          <t>MFA Printmaking</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -39762,11 +39380,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://www.mikaobayashi.com/</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39780,20 +39394,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Personal site found via web search (mikaobayashi.com) but no email visible — only Instagram and a /contact link; no email found</t>
+          <t>No email found via web search — only a LinkedIn profile surfaced, no personal site</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Heather Swenson</t>
+          <t>Ruoxua Fan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Painting</t>
+          <t>MFA Fine Arts</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -39822,13 +39436,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sophia Dell'Arciprete</t>
+          <t>Dora Moghaddamikhomami</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Photography</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -39836,11 +39450,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://sophiadellarciprete.com/</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39854,20 +39464,20 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Personal site found via web search (sophiadellarciprete.com) but no email visible in static HTML; no email found</t>
+          <t>No email found via web search — no personal site surfaced</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ari Zuaro</t>
+          <t>Marissa Raybuck</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Ceramics</t>
+          <t>MFA Graphic Design</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -39875,11 +39485,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://arizuaro.com/</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Temple/Tyler</t>
@@ -39893,667 +39499,17 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Personal site found via web search (arizuaro.com) but no email visible — only Instagram link; no email found</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Theodora Dagkli Andonopoulos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MFA Painting</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced, only a LinkedIn profile</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jess Lauro</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Esther Park</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Mollie Hansen</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Maedeh Mehdipour</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MFA Fiber and Material Studies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://maedehmehdipour.com/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Personal site found via web search (maedehmehdipour.com) but returned HTTP 403 on fetch — could not retrieve email; try visiting manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ally Messer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MFA Printmaking</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>No email found via web search — only a LinkedIn profile surfaced, no personal site</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Madeline Rodriguez</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Ruoxua Fan</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ivy Jewell</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Angelique Scott</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ben Solo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://www.bensoloart.com/</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Own site (bensoloart.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Logan Crompton</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://scoby.page/log3y-logan-crompton</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Link-in-bio page (scoby.page) found via web search — not fetched for email this pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Boi Boy</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced (full name may be 'Boi Boy Cottrell' per one source)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Diego Juarez</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MFA Painting</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://www.diegojuarez.com/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Personal site found via web search (diegojuarez.com/bio) but no email visible — only Instagram link and a /contact link not checked; no email found</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Gianna Santucci</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MFA Painting</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dora Moghaddamikhomami</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MFA Graphic Design</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>No email found via web search — no personal site surfaced</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marissa Raybuck</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MFA Graphic Design</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
           <t>No email found via web search — no personal site surfaced; works at Running Press Book Publishers</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Pegah Saebi</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MFA Design</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://pegahsaebi.com/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Temple/Tyler</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Own site (pegahsaebi.com) found via web search but could not be resolved by this tool's fetcher (DNS failure) — try visiting manually</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I30"/>
+  <autoFilter ref="A5:I12"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -26893,7 +26893,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+          <t>https://www.creatingbyjenna.art/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -26919,7 +26919,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>Personal site found via web search (creatingbyjenna.art) but no email visible — only Instagram/TikTok/YouTube and an unfetched /contact page; no email found</t>
         </is>
       </c>
     </row>
@@ -27010,7 +27010,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://students.colum.edu/ssac/exhibition-archives/Manifest-Exhibitions/2026/human-condition-2026-babfa-in-fine-art-exhibition</t>
+          <t>https://shop.colum.edu/lobotomy-by-ana-lara.html</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -27036,7 +27036,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>Confirmed as a Columbia Fine Arts student via ShopColumbia listing ('Lobotomy' by Ana Lara) but no email found — ShopColumbia has no direct artist contact page</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27166,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BFA/BA Fine Art (C33 Gallery)</t>
+          <t>BFA Fine Art (C33 Gallery)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -27192,7 +27192,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name only, from 'C33 Gallery' exhibitor list on the Human Condition 2026 BA/BFA Fine Art Exhibition page; no email/portfolio published</t>
+          <t>No email found — multiple different people share this name online (a Chicago mixed-media artist, a UIC student, a musician endorser); none confirmed as the same Columbia College Chicago student, so not treated as a match</t>
         </is>
       </c>
     </row>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iowa" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UW Art" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BGSU" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CalArts Animation" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RIT'!$A$5:$I$6</definedName>
@@ -59,6 +60,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Iowa'!$A$5:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'UW Art'!$A$5:$I$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'CalArts Animation'!$A$5:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28530,6 +28532,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source: CalArts Film/Video Animation Student Portfolios, 2026 — Character Animation (BFA 1-4, Affiliates, Recent Alumni) and Experimental Animation (BFA 1-4, MFA 1-3, Recent Alumni), 14 pages total. Each student entry includes name, class year, specialization, and Resume/Email/Portfolio/social links in plain static HTML (no JS rendering needed). Distinct from the separate 'CalArts' source (High Pass BFA exhibition, names only, no email).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>URL: https://calarts.edu/filmvideo/animation-student-portfolios/2026/character-animation and .../experimental-animation (14 sub-pages: bfa-1 through bfa-4, affiliates, recent-alumni, mfa-1 through mfa-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Accessed: 2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>graduation_year</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>portfolio_url</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>contacted</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I6"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -42,7 +42,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Otis'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Parsons'!$A$5:$I$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Temple-Tyler'!$A$5:$I$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VCU'!$A$5:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VCU'!$A$5:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Yale'!$A$5:$I$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UW-Madison'!$A$5:$I$7</definedName>
@@ -39627,7 +39627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -39740,7 +39740,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — LinkedIn, Pinterest, Facebook, and ethicaljewelry.org VCU chapter page all confirmed her identity (metal/glass artist, Craft/Material Studies MFA) but none published a direct email; no personal portfolio site found</t>
         </is>
       </c>
     </row>
@@ -39775,20 +39775,20 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found — confirmed real via VCU Scholars Compass thesis record and VCUarts Sculpture Instagram feature; aneuscheler.info found but appears to be an unrelated site with no VCU/contact content; no personal portfolio site found</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aya Khalife</t>
+          <t>Suzy Lykins</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -39810,20 +39810,20 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>Name corrected from 'Suzy Slykin' (source ICA caption misspelling) to 'Suzy Lykins', confirmed via matching thesis title 'Post Opera' on VCU Scholars Compass (scholarscompass.vcu.edu/etd/7995/). No email found via web search — no personal site/social found under correct spelling</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Suzy Slykin</t>
+          <t>Diego Pablo Málaga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -39845,20 +39845,20 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real (BFA 2021 UCF, painter) via ArtFields competition page and Instagram, but no personal portfolio site found and no email published anywhere</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rebecca Oh</t>
+          <t>Aleckxi Hristou-Dorhofer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Craft/Material Studies</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -39880,20 +39880,20 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real via MutualArt profile and LinkedIn (Textile Artist and Designer), but no personal portfolio site found and no email published anywhere</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>David Guarnizo</t>
+          <t>brooklin grantz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Craft/Material Studies</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -39915,20 +39915,20 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — confirmed real (BFA Ceramics, Indiana University Southeast 2020) via Alma's Gallery product page and Instagram (@brooklingrantzceramics), but no personal website found and no email published anywhere</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tyna Ontko</t>
+          <t>Alex Bacon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFA Fine Arts</t>
+          <t>MFA Painting and Printmaking</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -39950,227 +39950,17 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Diego Pablo Málaga</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Aleckxi Hristou-Dorhofer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>brooklin grantz</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Molly Garrett</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alex Bacon</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page (collaborative piece, multiple credited artists); likely incomplete relative to full graduating cohort</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Amy Duval</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VCU</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Name only, from artwork photo caption credit on ICA exhibition page; likely incomplete relative to full graduating cohort</t>
+          <t>No email found via web search — common name causes ambiguity (an unrelated NYC art historian also named Alex Bacon has a similar-looking alex-bacon.com site, confirmed NOT this person). Confirmed real via VCU Scholars Compass thesis 'Wiring Attachment' by Alexander Kunin Bacon and Bond Millen Gallery bio, but no personal site/email found for the correct person</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I18"/>
+  <autoFilter ref="A5:I12"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -46,7 +46,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Yale'!$A$5:$I$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'CMU'!$A$5:$I$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'UW-Madison'!$A$5:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ohio State'!$A$5:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ohio State'!$A$5:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Pratt'!$A$5:$I$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'BU'!$A$5:$I$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'SVA'!$A$5:$I$90</definedName>
@@ -886,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mandy Darrington</t>
+          <t>Annelise Duque</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.annelise-duque.com/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1003,14 +1003,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site annelise-duque.com found (CV/contact pages checked directly and via interactive Playwright probe), only Squarespace placeholder text present, no personal email published</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Annelise Duque</t>
+          <t>Breana Hendricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -1042,14 +1042,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — confirmed real (ceramic artist, Bronx NY, BFA SUNY New Paltz) via Instagram and Clay Art Center residency mentions; OSU directory profile page 404s, no personal site found</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>William Evans</t>
+          <t>Josiah Jamison</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.josiahjamison.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1081,14 +1081,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site josiahjamison.com found (about/CV pages checked), only Squarespace placeholder text present, no personal email published</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Breana Hendricks</t>
+          <t>Matty Machado</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1120,14 +1120,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found via web search — no personal site surfaced; note a 'Matthew Machado' also appears as an OSU Art Department Lecturer, possibly the same person post-graduation, but not confirmed as the same identity so not used</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Josiah Jamison</t>
+          <t>Zaza Naylor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://livablefuturesnow.org/zazanaylor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1159,20 +1159,20 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — confirmed real (Zachary Naylor, b. 1993 Waterbury CT) via Livable Futures artist page, only Squarespace placeholder text present; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matty Machado</t>
+          <t>Julian Robbins</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>MFA Art and Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>http://www.julianrobbins.art/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1198,14 +1198,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site julianrobbinsart.wordpress.com/julianrobbins.art found, checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andrew Mehall</t>
+          <t>Isabella Saraceni</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.isabellasaraceni.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1237,20 +1237,20 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site isabellasaraceni.com found, checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zaza Naylor</t>
+          <t>Alex Trippe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>MFA Studio Art (Ceramics)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://www.alextrippe.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1276,14 +1276,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found — own site alextrippe.com found (full name Alexandra Trippe), checked via interactive Playwright probe, no email/contact affordance found; OSU directory profile page 404s</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ivan David Ng</t>
+          <t>James Waite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1315,14 +1315,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>No email found via web search — confirmed real via First-Year MFA Show and Desire Lines exhibition mentions, but no personal site found and no email published anywhere</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julian Robbins</t>
+          <t>Shaheen Banerjee</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://uas.osu.edu/events/waiting-light-change</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1354,14 +1354,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Isabella Saraceni</t>
+          <t>Maria Beardsley</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://uas.osu.edu/events/waiting-light-change</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1393,14 +1393,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alex Trippe</t>
+          <t>Onni Conlon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://uas.osu.edu/events/waiting-light-change</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1432,14 +1432,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>James Waite</t>
+          <t>Samuel Estabrook</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://art.osu.edu/events/mfa-thesis-exhibition-desire-lines</t>
+          <t>https://uas.osu.edu/events/waiting-light-change</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1471,14 +1471,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name only, from 'Participating Artists' list; no email/portfolio published on source page</t>
+          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shaheen Banerjee</t>
+          <t>Takahiro Lo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maria Beardsley</t>
+          <t>Shruti Okubo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Onni Conlon</t>
+          <t>Sam Shankar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Samuel Estabrook</t>
+          <t>Xuan Wrigglesworth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1631,169 +1631,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Takahiro Lo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://uas.osu.edu/events/waiting-light-change</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Shruti Okubo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://uas.osu.edu/events/waiting-light-change</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sam Shankar</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://uas.osu.edu/events/waiting-light-change</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Xuan Wrigglesworth</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://uas.osu.edu/events/waiting-light-change</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ohio State</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>UNVERIFIED name reconstruction: source page lists names as ambiguous run-on text mixing 'Lastname, Firstname' and 'Firstname Lastname' with no reliable delimiter; double-check against the source page before using</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:I26"/>
+  <autoFilter ref="A5:I22"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -68,10 +68,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'BGSU'!$A$5:$J$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'CalArts Animation'!$A$5:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'UAL Central Saint Martins'!$A$5:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Alfred University'!$A$5:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Cornell'!$A$5:$J$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'UT Austin'!$A$5:$J$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Cooper Union'!$A$5:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Alfred University'!$A$5:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Cornell'!$A$5:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'UT Austin'!$A$5:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Cooper Union'!$A$5:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'SCAD'!$A$5:$J$372</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28823,7 +28823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -28914,13 +28914,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Amanda Gentry</t>
+          <t>Justin Donica</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MFA Ceramic Art</t>
+          <t>MFA Painting</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -28946,7 +28946,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (Fosdick-Nelson Gallery, opened April 4 2026); no email/portfolio published</t>
+          <t>Name from 2026 MFA Thesis Shows press release (joint exhibition 'Homebody' with Ignacio Luera, opened April 11 2026); no email/portfolio published</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -28954,13 +28954,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Max Heaton</t>
+          <t>Krist Lee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MFA Painting</t>
+          <t>MFA Sculpture-Dimensional Studies (glass focus)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -28986,7 +28986,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (Fosdick-Nelson Gallery, opened April 4 2026); no email/portfolio published</t>
+          <t>Name from 2026 MFA Thesis Shows press release (opened April 11 2026); no email/portfolio published</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -28994,13 +28994,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hazel Liu</t>
+          <t>Elizabeth Scott</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFA Electronic Integrated Arts</t>
+          <t>MFA Ceramic Art</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
+          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/2026-senior-thesis-shows-continue-with-pair-of-exhibitions-in-fosdick-nelson-gallery.cfm</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -29026,7 +29026,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (Turner Gallery, opened April 4 2026); no email/portfolio published</t>
+          <t>Name from 2026 MFA Thesis Shows press release ('I see / you mean', Fosdick-Nelson Gallery, May 8-16 2026); no email/portfolio published</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -29034,23 +29034,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Yuxuan Wang</t>
+          <t>Michelle Seo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFA Electronic Integrated Arts</t>
+          <t>MFA Ceramic Art</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
+          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -29066,7 +29066,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (Turner Gallery, opened April 4 2026); no email/portfolio published</t>
+          <t>Name from 2025 MFA Thesis Exhibitions event page (Cohen/Turner/Fosdick-Nelson Galleries, weekly Saturday openings April 5-May 9 2025); no email/portfolio published</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -29074,7 +29074,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Justin Donica</t>
+          <t>David Park</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -29085,12 +29085,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
+          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -29106,7 +29106,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (joint exhibition 'Homebody' with Ignacio Luera, opened April 11 2026); no email/portfolio published</t>
+          <t>Name from 2025 MFA Thesis Exhibitions event page; no email/portfolio published</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -29114,23 +29114,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ignacio Luera</t>
+          <t>Erin Berry</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Painting</t>
+          <t>MFA Ceramic Art</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
+          <t>http://erin-berry.com/bio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -29146,338 +29146,18 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name from 2026 MFA Thesis Shows press release (joint exhibition 'Homebody' with Justin Donica, opened April 11 2026); no email/portfolio published</t>
+          <t>Name from 2025 MFA Thesis Exhibitions event page. Has own site (erin-berry.com/bio) but it's DNS-unreachable by this tool's fetchers (ENOTFOUND) -- worth a manual check for a contact email. Instagram @eeberry (2,778 followers), also recently won the 2026 Winifred Shantz Award for Ceramics</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Krist Lee</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MFA Sculpture-Dimensional Studies (glass focus)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Name from 2026 MFA Thesis Shows press release (opened April 11 2026); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GH Wood</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MFA Ceramic Art</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/nyscc-at-alfred-university-set-to-host-2026-mfa-thesis-shows.cfm</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Name from 2026 MFA Thesis Shows press release (opened April 11 2026); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Marita Manson</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MFA Ceramic Art</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/2026-senior-thesis-shows-continue-with-pair-of-exhibitions-in-fosdick-nelson-gallery.cfm</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Name from 2026 MFA Thesis Shows press release ('The Call is Coming from Inside the House', Fosdick-Nelson Gallery, May 8-16 2026); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Elizabeth Scott</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MFA Ceramic Art</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/about/news/pressreleases/general/2026/2026-senior-thesis-shows-continue-with-pair-of-exhibitions-in-fosdick-nelson-gallery.cfm</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Name from 2026 MFA Thesis Shows press release ('I see / you mean', Fosdick-Nelson Gallery, May 8-16 2026); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Michelle Seo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MFA Ceramic Art</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Name from 2025 MFA Thesis Exhibitions event page (Cohen/Turner/Fosdick-Nelson Galleries, weekly Saturday openings April 5-May 9 2025); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Toomas Toomepuu</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MFA Sculpture-Dimensional Studies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Name from 2025 MFA Thesis Exhibitions event page; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>David Park</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MFA Painting</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Name from 2025 MFA Thesis Exhibitions event page; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Erin Berry</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MFA Ceramic Art</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://www.alfred.edu/student-life/events/calendar/2025/04/mfa-thesis-exhibitions.html</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Alfred University</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Name from 2025 MFA Thesis Exhibitions event page; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:J19"/>
+  <autoFilter ref="A5:J11"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29491,7 +29171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29702,7 +29382,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Smith Galtney</t>
+          <t>Breanna Maxine</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -29742,7 +29422,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jacquelyn Johnson</t>
+          <t>Angela Rauf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -29782,7 +29462,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Breanna Maxine</t>
+          <t>Caroline Wallis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -29822,7 +29502,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jared Radin</t>
+          <t>Monique Flynn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -29838,7 +29518,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/beyond-aap/m-f-a-image-text-26-thesis-show-self-assembly/</t>
+          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-image-text/image-text-student-profiles/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -29854,7 +29534,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Name from MFA Image Text '26 thesis show 'SELF/ASSEMBLY'; no email/portfolio published</t>
+          <t>Name added from Cornell's official MFA Image Text Student Profiles directory page (11-person '26 cohort) -- missing from the original SELF/ASSEMBLY thesis-show-based list; no email/portfolio published</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -29862,7 +29542,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joseph Rafferty III</t>
+          <t>Clare Sheedy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -29878,7 +29558,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/beyond-aap/m-f-a-image-text-26-thesis-show-self-assembly/</t>
+          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-image-text/image-text-student-profiles/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -29894,7 +29574,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Name from MFA Image Text '26 thesis show 'SELF/ASSEMBLY'; no email/portfolio published</t>
+          <t>Name added from Cornell's official MFA Image Text Student Profiles directory page (11-person '26 cohort) -- missing from the original SELF/ASSEMBLY thesis-show-based list; no email/portfolio published</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -29902,13 +29582,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Angela Rauf</t>
+          <t>Marissa Cote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFA Image Text</t>
+          <t>MFA Creative Visual Arts</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -29918,7 +29598,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/beyond-aap/m-f-a-image-text-26-thesis-show-self-assembly/</t>
+          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -29934,7 +29614,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name from MFA Image Text '26 thesis show 'SELF/ASSEMBLY'; no email/portfolio published</t>
+          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -29942,13 +29622,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Caroline Wallis</t>
+          <t>Michael Morgan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFA Image Text</t>
+          <t>MFA Creative Visual Arts</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -29958,7 +29638,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/beyond-aap/m-f-a-image-text-26-thesis-show-self-assembly/</t>
+          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -29974,7 +29654,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name from MFA Image Text '26 thesis show 'SELF/ASSEMBLY'; no email/portfolio published</t>
+          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -29982,7 +29662,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marissa Cote</t>
+          <t>Faye Pamintuan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -30022,23 +29702,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carla Rangel García</t>
+          <t>Hanul Gu</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -30054,7 +29734,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; also appears in 'Space of Becoming' sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -30062,23 +29742,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Michael Morgan</t>
+          <t>Julien Roumieu-Lavigne</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -30094,7 +29774,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -30102,23 +29782,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onome Olotu</t>
+          <t>Won Ryu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -30134,7 +29814,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -30142,23 +29822,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Faye Pamintuan</t>
+          <t>Edward Conte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -30174,7 +29854,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; also appears in 'Space of Becoming' sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -30182,23 +29862,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sandy Wang</t>
+          <t>Rachel Shepherd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -30214,7 +29894,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -30222,23 +29902,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sheila Novak</t>
+          <t>Kate James</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MFA Creative Visual Arts</t>
+          <t>BFA Fine Arts</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/art/master-of-fine-arts-in-creative-visual-arts/</t>
+          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -30254,7 +29934,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Name from MFA Creative Visual Arts '26 cohort (search-indexed); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -30262,7 +29942,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sally Yu</t>
+          <t>Vera Kelly</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -30294,7 +29974,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition' (9 seniors); no email/portfolio published</t>
+          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -30302,7 +29982,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lena Park</t>
+          <t>Alex Park</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -30318,7 +29998,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/news-events/exhibition/group-exhibition-space-becoming</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -30334,7 +30014,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; also appears in 'Space of Becoming' sub-show; no email/portfolio published</t>
+          <t>Name from BFA '25 sub-show 'Space of Becoming' (not in the main 9-person Thesis Group Exhibition list); no email/portfolio published</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -30342,7 +30022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hanul Gu</t>
+          <t>Bella H Chung</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -30358,7 +30038,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -30374,7 +30054,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; also appears in 'Space of Becoming' sub-show; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -30382,7 +30062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Julien Roumieu-Lavigne</t>
+          <t>Julie Christine Chung</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -30398,7 +30078,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -30414,7 +30094,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -30422,7 +30102,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Won Ryu</t>
+          <t>Josephine Cosmosse</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -30438,7 +30118,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -30454,7 +30134,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -30462,7 +30142,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Edward Conte</t>
+          <t>AnneMarie Ehrenreich</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -30478,7 +30158,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -30494,7 +30174,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; also appears in 'Space of Becoming' sub-show; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -30502,7 +30182,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rachel Shepherd</t>
+          <t>Rory Haltmaier</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -30518,7 +30198,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -30534,7 +30214,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -30542,7 +30222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kate James</t>
+          <t>Amy Lee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -30558,7 +30238,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -30574,7 +30254,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
+          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; also appears in 'Space of Becoming'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -30582,7 +30262,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vera Kelly</t>
+          <t>Erin Choi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -30593,12 +30273,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/thesis-group-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -30614,7 +30294,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Name from BFA '25 Senior Thesis 'Thesis Group Exhibition'; no email/portfolio published</t>
+          <t>Name from BFA '26 thesis sub-show 'with a trace' (Bibliowicz Family Gallery, May 19-24 2026); no email/portfolio published</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -30622,7 +30302,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alex Park</t>
+          <t>Nadia Holcomb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -30633,12 +30313,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/news-events/exhibition/group-exhibition-space-becoming</t>
+          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -30654,7 +30334,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Name from BFA '25 sub-show 'Space of Becoming' (not in the main 9-person Thesis Group Exhibition list); no email/portfolio published</t>
+          <t>Name from BFA '26 thesis sub-show 'with a trace'; no email/portfolio published</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -30662,7 +30342,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bella H Chung</t>
+          <t>NEBA Onajevwe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -30673,12 +30353,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
+          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -30694,378 +30374,18 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
+          <t>Name from BFA '26 thesis sub-show 'with a trace'; source lists as one name 'NEBA Onajevwe' (a search summary mis-split this into two separate names in one pass); no email/portfolio published</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Julie Christine Chung</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Josephine Cosmosse</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AnneMarie Ehrenreich</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Rory Haltmaier</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Amy Lee</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/senior-b-f-a-thesis-exhibition/</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Name from a separate 'Senior B.F.A. Thesis Exhibition' 6-person sub-show; also appears in 'Space of Becoming'; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Erin Choi</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Name from BFA '26 thesis sub-show 'with a trace' (Bibliowicz Family Gallery, May 19-24 2026); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Nadia Holcomb</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Name from BFA '26 thesis sub-show 'with a trace'; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Asuka Kurebayashi</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Name from BFA '26 thesis sub-show 'with a trace'; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEBA Onajevwe</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>BFA Fine Arts</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://aap.cornell.edu/events/exhibition/b-f-a-thesis-with-a-trace/</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Cornell</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Name from BFA '26 thesis sub-show 'with a trace'; source lists as one name 'NEBA Onajevwe' (a search summary mis-split this into two separate names in one pass); no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:J42"/>
+  <autoFilter ref="A5:J33"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32947,7 +32267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -33038,7 +32358,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nathan Anthony</t>
+          <t>Lorena Diosdado</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -33070,7 +32390,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition (14 grads, Visual Arts Center, April 18-May 10 2025); no email/portfolio published</t>
+          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -33078,7 +32398,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ben Copolillo</t>
+          <t>Laurent Le Bel–Roux</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -33118,7 +32438,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Noah Dasho</t>
+          <t>Miles Matis–Uzzo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -33158,7 +32478,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lorena Diosdado</t>
+          <t>Britt Moseley</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -33198,7 +32518,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Christian Hastad</t>
+          <t>Sasha-Kay Nicole</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -33238,13 +32558,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tova Katzman</t>
+          <t>Javier Robelo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFA Studio Art (Photography and Video)</t>
+          <t>MFA Studio Art</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -33270,7 +32590,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; discipline (photography/video) confirmed via a second-year MFA mention in search results; no email/portfolio published</t>
+          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -33278,7 +32598,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Laurent Le Bel–Roux</t>
+          <t>Phoebe Shuman–Goodier</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -33318,7 +32638,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Miles Matis–Uzzo</t>
+          <t>Katherine Vaughn</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -33358,7 +32678,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Britt Moseley</t>
+          <t>Maya Gauvin</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -33369,12 +32689,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -33390,7 +32710,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -33398,7 +32718,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sasha-Kay Nicole</t>
+          <t>Edward Gia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -33409,12 +32729,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -33430,7 +32750,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -33438,7 +32758,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Javier Robelo</t>
+          <t>Morgan Grigsby</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -33449,12 +32769,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -33470,7 +32790,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -33478,7 +32798,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Phoebe Shuman–Goodier</t>
+          <t>Tiffany Katarina Smith</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -33489,12 +32809,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -33510,7 +32830,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -33518,23 +32838,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Katherine Vaughn</t>
+          <t>Mayya Al-Harthy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -33550,7 +32870,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition (large BFA cohort, painting/drawing/print/sculpture/video/photography, Visual Arts Center); no email/portfolio published</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -33558,23 +32878,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Selina Wagner</t>
+          <t>Joselinne Amador</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/acceleration-without-arrival-2025-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -33590,7 +32910,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Name from 'Acceleration Without Arrival' 2025 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -33598,13 +32918,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rosalyn Jewel Farney</t>
+          <t>Mabel Andrae</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -33614,7 +32934,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -33630,7 +32950,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition (7 grads, photography/painting/print/sculpture, Visual Arts Center, April 17-May 9 2026); no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -33638,13 +32958,13 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maya Gauvin</t>
+          <t>Kyla Antonio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -33654,7 +32974,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -33670,7 +32990,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -33678,13 +32998,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Edward Gia</t>
+          <t>Anastasia Balabayev</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -33694,7 +33014,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -33710,7 +33030,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -33718,13 +33038,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Morgan Grigsby</t>
+          <t>Tucker Bassett</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -33734,7 +33054,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -33750,7 +33070,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -33758,13 +33078,13 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jo Kim</t>
+          <t>Nahla Marulanda Beltran</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -33774,7 +33094,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -33790,7 +33110,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -33798,13 +33118,13 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tiffany Katarina Smith</t>
+          <t>Justin Billey</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -33814,7 +33134,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -33830,7 +33150,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -33838,13 +33158,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nolan Zunk</t>
+          <t>Juliana Penna Brandao</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MFA Studio Art</t>
+          <t>BFA Studio Art</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -33854,7 +33174,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://utvac.org/event/half-second-or-less-2026-studio-art-mfa-thesis-exhibition</t>
+          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -33870,7 +33190,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Name from 'Half a Second or Less' 2026 Studio Art MFA Thesis Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -33878,7 +33198,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mayya Al-Harthy</t>
+          <t>Avery Bryan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -33910,7 +33230,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition (large BFA cohort, painting/drawing/print/sculpture/video/photography, Visual Arts Center); no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -33918,7 +33238,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Joselinne Amador</t>
+          <t>Lydia Butts</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -33958,7 +33278,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mabel Andrae</t>
+          <t>Jacob Cardenas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -33998,7 +33318,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kyla Antonio</t>
+          <t>Cleo Chaney</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -34038,7 +33358,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anastasia Balabayev</t>
+          <t>Ella Cheesar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -34078,7 +33398,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tucker Bassett</t>
+          <t>Scott Cobb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -34118,7 +33438,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nahla Marulanda Beltran</t>
+          <t>Kate Crowder</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -34158,7 +33478,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Justin Billey</t>
+          <t>Ania Davila</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -34198,7 +33518,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Juliana Penna Brandao</t>
+          <t>Ellie Davila</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -34238,7 +33558,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Josiah Brown</t>
+          <t>Ankitha Doma</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -34278,7 +33598,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Avery Bryan</t>
+          <t>Thania Elizalde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -34318,7 +33638,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lydia Butts</t>
+          <t>Fionayuko Forbes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -34358,7 +33678,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jacob Cardenas</t>
+          <t>Kaelie Galvan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -34398,7 +33718,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cleo Chaney</t>
+          <t>Irina Griffin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -34438,7 +33758,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ella Cheesar</t>
+          <t>Genavieve G.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -34470,7 +33790,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; last name truncated on the source page (shown only as 'G.') and not recoverable; no email/portfolio published</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -34478,7 +33798,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jeongin Choi</t>
+          <t>Dylan Haefner</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -34518,7 +33838,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Scott Cobb</t>
+          <t>Tyson Humbert</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -34558,7 +33878,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kate Crowder</t>
+          <t>Farwah Hussain</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -34598,7 +33918,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ania Davila</t>
+          <t>Alexis Ikemba</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -34638,7 +33958,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ellie Davila</t>
+          <t>Erin Jackson</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -34678,7 +33998,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gabrielle Dick</t>
+          <t>Leslie Dawn Johnson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -34718,7 +34038,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ankitha Doma</t>
+          <t>Mindy Kang</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -34758,7 +34078,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Thania Elizalde</t>
+          <t>Ji Kim</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -34798,7 +34118,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Reese Ertel</t>
+          <t>Elizabeth Minton</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -34838,7 +34158,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Claire Fleming</t>
+          <t>Kelly Munguia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -34878,7 +34198,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fionayuko Forbes</t>
+          <t>Natán Murillo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -34918,7 +34238,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kaelie Galvan</t>
+          <t>Alissa Murphy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -34958,7 +34278,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Irina Griffin</t>
+          <t>Estevan Nunez</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -34998,7 +34318,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Genavieve G.</t>
+          <t>Kate Phillips</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -35030,7 +34350,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; last name truncated on the source page (shown only as 'G.') and not recoverable; no email/portfolio published</t>
+          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -35038,7 +34358,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dylan Haefner</t>
+          <t>Chloe Pruett</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -35078,7 +34398,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tyson Humbert</t>
+          <t>Alejandra Quiroga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -35118,7 +34438,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Farwah Hussain</t>
+          <t>Caitlin Reimer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -35158,7 +34478,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alexis Ikemba</t>
+          <t>Alonso Rodriguez</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -35198,7 +34518,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Erin Jackson</t>
+          <t>Mariel Rojas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -35238,7 +34558,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Leslie Dawn Johnson</t>
+          <t>Austin Tharp</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -35278,7 +34598,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mindy Kang</t>
+          <t>Molly Thomason</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -35318,7 +34638,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ji Kim</t>
+          <t>Sydney Trautwein</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -35358,7 +34678,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elizabeth Minton</t>
+          <t>Genevieve Traynor</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -35398,7 +34718,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kelly Munguia</t>
+          <t>Azul Valles</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -35438,7 +34758,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Natán Murillo</t>
+          <t>Maia Vollbrecht</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -35478,7 +34798,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alissa Murphy</t>
+          <t>Olivia Wallace</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -35518,7 +34838,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Estevan Nunez</t>
+          <t>Shannon Leigh</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -35558,7 +34878,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kate Phillips</t>
+          <t>Renee Yu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -35595,573 +34915,13 @@
       </c>
       <c r="J69" t="inlineStr"/>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Chloe Pruett</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Alejandra Quiroga</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Caitlin Reimer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Alonso Rodriguez</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Mariel Rojas</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Austin Tharp</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Molly Thomason</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Sydney Trautwein</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Genevieve Traynor</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Azul Valles</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Maia Vollbrecht</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Olivia Wallace</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Shannon Leigh</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Renee Yu</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>BFA Studio Art</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>https://utvac.org/event/proof-life-2026-senior-art-exhibition</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>UT Austin</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Name from 'Proof of Life' 2026 Senior Art Exhibition; no email/portfolio published</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:J83"/>
+  <autoFilter ref="A5:J69"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -36175,7 +34935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -36263,93 +35023,13 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Skye Jones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BFA Art (HSS minor: History and Theory of Art)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://cooper.edu/about/news/class-2026-their-own-words</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Cooper Union</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Name from 'Class of 2026: In Their Own Words' article; confirmed School of Art via 'A'26' suffix. Creates installations; exhibited work titled 'Ornamental Child'. No email/portfolio published. Cooper Union's School of Art has no consolidated roster page (per tradition, work is attributed by artist name only, spread across annual End of Year Show photo captions mixing all 3 schools — Art/Architecture/Engineering — with no reliable way to distinguish School of Art students from the others without an explicit suffix)</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Regina Cervantes Ellis</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>BFA Art (HSS minor: History and Theory of Art)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://cooper.edu/about/news/class-2026-their-own-words</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Cooper Union</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Name from 'Class of 2026: In Their Own Words' article; confirmed School of Art via 'A'26' suffix. Researched Mexican Restaurant Graphic Design via the Rhoda Lubalin Fellowship; exhibited work titled 'Sandia, Sanoche'. No email/portfolio published.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:J7"/>
+  <autoFilter ref="A5:J6"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
+++ b/Dezi Art Prize Student Data Scraping/master_students_no_email.xlsx
@@ -72,7 +72,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Cornell'!$A$5:$J$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'UT Austin'!$A$5:$J$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Cooper Union'!$A$5:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'SCAD'!$A$5:$J$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'SCAD'!$A$5:$J$305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35043,7 +35043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J372"/>
+  <dimension ref="A1:J305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -35454,7 +35454,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jannelly Herrera</t>
+          <t>Henry McDonald</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -35486,7 +35486,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Pajara, An Investigation of the Feminine Experience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Water Resistant Cowboy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -35494,7 +35494,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sandra Iafrate</t>
+          <t>Cat Ward</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -35526,7 +35526,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Portrait of Past and Present'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Deep Dive'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -35534,7 +35534,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rachel Korzeb</t>
+          <t>Paola A. Badillo Pont</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -35566,7 +35566,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Imagination and Reality'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Inner Loom'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -35574,7 +35574,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Elise Le Gallo</t>
+          <t>Lynsi Boyd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Light is Like Water'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'A Natural History of Dreams'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -35614,7 +35614,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Henry McDonald</t>
+          <t>Michele Allen Fulkerson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -35646,7 +35646,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Water Resistant Cowboy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Will You Remember Me: Self-Portraits as Self-Evidence'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sharon Potter</t>
+          <t>Kayla D. Grayson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -35686,7 +35686,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'When 'Resilient' Becomes a Four-Letter Word: Living with the Aftermath'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Twice as Good'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -35694,7 +35694,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikki Rakov</t>
+          <t>Dave Hamann</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -35726,7 +35726,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'To Know, To Dare, To Keep Silent'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Nature: An Auspicious Aesthetic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -35734,7 +35734,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cat Ward</t>
+          <t>Briana Danyele Hunter</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -35766,7 +35766,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Deep Dive'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Raw Canvas &amp; Raw Honesty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -35774,7 +35774,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paola A. Badillo Pont</t>
+          <t>Mother Justina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -35806,7 +35806,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Inner Loom'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Prayer, Work, and Place'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -35814,7 +35814,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lynsi Boyd</t>
+          <t>Kelly Lewis</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -35846,7 +35846,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'A Natural History of Dreams'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Rewilding Kinship: Advocacy Through Joy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -35854,7 +35854,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Michele Allen Fulkerson</t>
+          <t>Chidera Maduabum</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -35886,7 +35886,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Will You Remember Me: Self-Portraits as Self-Evidence'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Expressive Depths of Color: A Personal Journey'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -35894,7 +35894,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kayla D. Grayson</t>
+          <t>Brandice Palmer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -35926,7 +35926,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Twice as Good'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Fly, Amanita &amp; Other Toxic Beauties'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -35934,7 +35934,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dave Hamann</t>
+          <t>Kexin Wang</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -35966,7 +35966,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Nature: An Auspicious Aesthetic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'My Dialogue with Caladiums'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -35974,7 +35974,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Briana Danyele Hunter</t>
+          <t>Maria Knuckley Robinson</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -36006,7 +36006,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Raw Canvas &amp; Raw Honesty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Lavender and Stone'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -36014,7 +36014,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mother Justina</t>
+          <t>Rik Speed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -36046,7 +36046,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Prayer, Work, and Place'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Bricklaying'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -36054,7 +36054,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cristina Marietta Komaroff</t>
+          <t>Samantha Allen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -36086,7 +36086,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Cristina's Gaze'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Indefatigable'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -36094,7 +36094,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kelly Lewis</t>
+          <t>Elizabeth Bizianes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -36126,7 +36126,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Rewilding Kinship: Advocacy Through Joy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Searching for Identity: An Adoption Story'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -36134,7 +36134,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chidera Maduabum</t>
+          <t>Hiromi Isobe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -36166,7 +36166,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Expressive Depths of Color: A Personal Journey'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Can I See?'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -36174,7 +36174,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shannon Meadows</t>
+          <t>Lauren Leep-Cabrera</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -36206,7 +36206,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'On Our Own Terms'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Edge of Perception'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -36214,7 +36214,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brandice Palmer</t>
+          <t>Wuci Yang</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -36246,7 +36246,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Fly, Amanita &amp; Other Toxic Beauties'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Memory in Motion: Exploring Fluidity in Transitional Spaces'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -36254,18 +36254,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Keshav Prasad</t>
+          <t>Paige M. Cunningham</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -36286,7 +36286,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Revelations of Food and History'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Station 92: A Sci-Fi and Horror Themed Dark Ride Attraction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -36294,18 +36294,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Evelyn Shoults</t>
+          <t>Danran Huang</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -36326,7 +36326,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Daily Dose: Ritual, Recovery, and the Unheard Patient'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Other Side of the Room Using the Stages of Cognitive Development in Children's Books to Make The'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -36334,18 +36334,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Joanna Silver</t>
+          <t>Kayla Degennaro</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -36366,7 +36366,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'What American Dream?'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Cult of the Cheerleaders: A Deep Dive into Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -36374,18 +36374,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kexin Wang</t>
+          <t>Fuhua Yang</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -36406,7 +36406,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'My Dialogue with Caladiums'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Framing the Game: Exploring Procedures and Trends in Creating Standardized Splash Art for Video Game'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -36414,18 +36414,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maria Knuckley Robinson</t>
+          <t>Qi Gao</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -36446,7 +36446,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Lavender and Stone'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Illustrating the Joy of Family Cooking in Children's Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -36454,18 +36454,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rik Speed</t>
+          <t>Gege Wang</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -36486,7 +36486,7 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Bricklaying'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Challenge of Sameness: Exploring Methods of Innovation in Game Animation Aesthetics'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -36494,18 +36494,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Samantha Allen</t>
+          <t>Dilzodakhon Khamidjonova</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -36526,7 +36526,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Indefatigable'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Zaynab is Calling: Illustrating Family Connection, Early Childhood Development, and Cultural Identit'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -36534,18 +36534,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Elizabeth Bizianes</t>
+          <t>Anna Levy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -36566,7 +36566,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Searching for Identity: An Adoption Story'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'A Is for Alligators Using Defibrillators: An Exploration of Visual and Verbal Nonsense in Creating a'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -36574,18 +36574,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Denis Byrd</t>
+          <t>Zhuosheng Li</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -36606,7 +36606,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Sehnsucht: Longing and Joy in the Southern Landscape'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Pixel Art as a Lasting Indie Game Language'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -36614,18 +36614,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hiromi Isobe</t>
+          <t>Junyi Ma</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -36646,7 +36646,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Can I See?'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Packaging: Visual Impact and Product Identity Expression'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -36654,18 +36654,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lauren Leep-Cabrera</t>
+          <t>Eric Pung</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -36686,7 +36686,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Edge of Perception'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Artificial Inanity: The Folly of Generative AI in Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -36694,18 +36694,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hannah Grace Maki</t>
+          <t>Samantha Shields-Travers</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -36726,7 +36726,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Duality of Reality'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Drawing Laughs: Visual Humor in Children's Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -36734,18 +36734,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jazmin Marie Saunders</t>
+          <t>Rongshuyue Sun</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -36766,7 +36766,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Sucrose'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Visualizing Chinese Idioms: Rediscovering the Essence of Traditional Chinese Culture'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -36774,18 +36774,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wuci Yang</t>
+          <t>Toni Weldon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Painting (SCAD)</t>
+          <t>Illustration (SCAD)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -36806,7 +36806,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Memory in Motion: Exploring Fluidity in Transitional Spaces'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Soul Tether: A Creature Compendium'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -36814,7 +36814,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Paige M. Cunningham</t>
+          <t>Aria Zhang</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -36846,7 +36846,7 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Station 92: A Sci-Fi and Horror Themed Dark Ride Attraction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Where the Line Divides: Visual Priorities in Decorative and Narrative Ink Drawing'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -36854,7 +36854,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Danran Huang</t>
+          <t>Courtney Brown</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -36886,7 +36886,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Other Side of the Room Using the Stages of Cognitive Development in Children's Books to Make The'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Crayola Cuties: Reimagining Food &amp; Resource Security for Public Elementary Schools Through Brand Col'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -36894,7 +36894,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kayla Degennaro</t>
+          <t>Eddy Burte</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -36926,7 +36926,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Cult of the Cheerleaders: A Deep Dive into Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Sung Through Time: Telling Jewish Stories Through Concept Art'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -36934,7 +36934,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fuhua Yang</t>
+          <t>María Camila Girón</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -36945,7 +36945,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -36966,7 +36966,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Framing the Game: Exploring Procedures and Trends in Creating Standardized Splash Art for Video Game'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Reimagining the Caiman: Colombian Folklore for Illustrated Children's Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -36974,7 +36974,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Qi Gao</t>
+          <t>Wenjun Guo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -36985,7 +36985,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -37006,7 +37006,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Illustrating the Joy of Family Cooking in Children's Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Illustrating the I Ching: Card Designs Inspired by History for Cultural Transmission'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -37014,7 +37014,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gege Wang</t>
+          <t>Emily Rae Hester</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -37025,7 +37025,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -37046,7 +37046,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Challenge of Sameness: Exploring Methods of Innovation in Game Animation Aesthetics'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Conservation Illustrations: How Illustrations Use Psychology to Affect, Inform, and Educate Society'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -37054,7 +37054,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dilzodakhon Khamidjonova</t>
+          <t>Yifei Hou</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -37065,7 +37065,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -37086,7 +37086,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Zaynab is Calling: Illustrating Family Connection, Early Childhood Development, and Cultural Identit'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Exploring the Role of Stylized Art in Character Design: Cultural Exploration and Visual Engagement'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -37094,7 +37094,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Anna Levy</t>
+          <t>Madelyn Kimber</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -37126,7 +37126,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'A Is for Alligators Using Defibrillators: An Exploration of Visual and Verbal Nonsense in Creating a'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Paws, Pages, and Perspective: Anthropomorphism as a Reflection of Human Nature'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -37134,7 +37134,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zhuosheng Li</t>
+          <t>Hyon Lee</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -37145,7 +37145,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -37166,7 +37166,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Pixel Art as a Lasting Indie Game Language'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'How Visual Storytelling Allows Us to Understand Emotion to Improve Mental Health'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -37174,7 +37174,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junyi Ma</t>
+          <t>Chia Jou Lin</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -37206,7 +37206,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Packaging: Visual Impact and Product Identity Expression'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Art of Self: Establishing Illustration Language Through Learning and Experimentation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -37214,7 +37214,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Eric Pung</t>
+          <t>Sophia Litwak</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -37225,7 +37225,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -37246,7 +37246,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Artificial Inanity: The Folly of Generative AI in Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Discovering Possibilities for Beauty in Everything: Radical Self-Healing Through Tarot'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -37254,7 +37254,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Samantha Shields-Travers</t>
+          <t>Jingchu Lu</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -37265,7 +37265,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -37286,7 +37286,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Drawing Laughs: Visual Humor in Children's Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Research on Commercialization Strategies for Picture Books: A Comparative Study of China and North A'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -37294,7 +37294,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Connor Stelle</t>
+          <t>Menghan Wang</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -37305,7 +37305,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -37326,7 +37326,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Kingdom of Shadows: Reimagining Silent Horror Films Through Traditional Inking Techniques'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Silent Art of Visual Narration : Exploring Narrativity and Emotional Expression in Wordless Pict'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -37334,7 +37334,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rongshuyue Sun</t>
+          <t>Alejandro Martinez</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -37345,7 +37345,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -37366,7 +37366,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Visualizing Chinese Idioms: Rediscovering the Essence of Traditional Chinese Culture'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'From Wyeth to Frazetta: A Study and Analysis of Fantasy Art in 20th Century Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
@@ -37374,7 +37374,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Toni Weldon</t>
+          <t>Leslie Osmont</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -37385,7 +37385,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -37406,7 +37406,7 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Soul Tether: A Creature Compendium'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Designing Place: Fostering Sustainability Through Surface Design &amp; Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
@@ -37414,7 +37414,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Aria Zhang</t>
+          <t>Kolbe Pitts</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -37425,7 +37425,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -37446,7 +37446,7 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Where the Line Divides: Visual Priorities in Decorative and Narrative Ink Drawing'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Records of Lymsa: Building Tools for Telling Stories'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
@@ -37454,7 +37454,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Courtney Brown</t>
+          <t>Yiran Qin</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -37465,7 +37465,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -37486,7 +37486,7 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Crayola Cuties: Reimagining Food &amp; Resource Security for Public Elementary Schools Through Brand Col'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The World on Screen: Application of Motion Graphics in E-books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -37494,7 +37494,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Eddy Burte</t>
+          <t>Emilie Seda</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -37505,7 +37505,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -37526,7 +37526,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Sung Through Time: Telling Jewish Stories Through Concept Art'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Illustration Pedagogy: How Teachers Employ Children's Books as a Pedagogical Tool to Improve Cogniti'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -37534,7 +37534,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chani Alia Becker</t>
+          <t>Yuxin Shang</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -37566,7 +37566,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Beneath the Surface: Depicting the Depths of Fairy Tales through Jungian-Psychology Informed Illustr'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Enriching Book Cover Illustration with Different Materials'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -37574,7 +37574,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>María Camila Girón</t>
+          <t>Audrey Song</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -37606,7 +37606,7 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Reimagining the Caiman: Colombian Folklore for Illustrated Children's Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Beyond Drawing Nature, Science and Culture: The Fusion of the Artist's Personal Style and Scientific'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -37614,7 +37614,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Wenjun Guo</t>
+          <t>Paul V. Thompson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -37646,7 +37646,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Illustrating the I Ching: Card Designs Inspired by History for Cultural Transmission'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Henny Penny and the Adult Picture Book Market'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
@@ -37654,7 +37654,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Emily Rae Hester</t>
+          <t>AyaBird Wu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -37686,7 +37686,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Conservation Illustrations: How Illustrations Use Psychology to Affect, Inform, and Educate Society'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'From the Perspective of Illustrators: Exploring Visual Narrative in Story Collection Adaptations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -37694,7 +37694,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Yifei Hou</t>
+          <t>Shiyao Yin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -37726,7 +37726,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Exploring the Role of Stylized Art in Character Design: Cultural Exploration and Visual Engagement'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Exploring How Decorative Elements Support Visual Storytelling in Illustrated Book'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J70" t="inlineStr"/>
@@ -37734,7 +37734,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Madelyn Kimber</t>
+          <t>Lingyan Zhang</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -37766,7 +37766,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Paws, Pages, and Perspective: Anthropomorphism as a Reflection of Human Nature'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Beyond the Senses: Exploring the Interactions and Impact of Vision and Olfaction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -37774,7 +37774,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hyon Lee</t>
+          <t>Yuanyuan Zhang</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -37806,7 +37806,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'How Visual Storytelling Allows Us to Understand Emotion to Improve Mental Health'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Hidden Palettes : Exploring the Fusion of Food and Urban Identity in China's Lesser-Known  Cities Th'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -37814,7 +37814,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Chia Jou Lin</t>
+          <t>Kathleen Burns</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -37846,7 +37846,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Art of Self: Establishing Illustration Language Through Learning and Experimentation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Everyday Ethnography: Illustrated Portraiture as Accessible Anthropology'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -37854,7 +37854,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sophia Litwak</t>
+          <t>Yuchen Cui</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -37886,7 +37886,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Discovering Possibilities for Beauty in Everything: Radical Self-Healing Through Tarot'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Influence of Dynamic Lighting and Color in Video Games on Image Mood and Player Emotion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -37894,7 +37894,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jingchu Lu</t>
+          <t>Jesse A Reese</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -37926,7 +37926,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Research on Commercialization Strategies for Picture Books: A Comparative Study of China and North A'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Shadows of Fear: A Look at the Use of Fear in Illustration as a Drive for Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -37934,7 +37934,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Menghan Wang</t>
+          <t>Amani Hoskin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -37966,7 +37966,7 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Silent Art of Visual Narration : Exploring Narrativity and Emotional Expression in Wordless Pict'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'From One 2 One: Twins and the Exploration of Media, Narrative and Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -37974,7 +37974,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alejandro Martinez</t>
+          <t>Yangyu Li</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -38006,7 +38006,7 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'From Wyeth to Frazetta: A Study and Analysis of Fantasy Art in 20th Century Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Storytelling Through Tactile Engagement: The Interactive Power of Artists’ Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -38014,7 +38014,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Leslie Osmont</t>
+          <t>María Rosa Angélica Ramos Berríos</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -38046,7 +38046,7 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Designing Place: Fostering Sustainability Through Surface Design &amp; Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Through the Glass: The Art of Belonging Through Puerto Rican Folklore and Surface Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -38054,7 +38054,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kolbe Pitts</t>
+          <t>Lauren Julianna Schermerhorn</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -38086,7 +38086,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Records of Lymsa: Building Tools for Telling Stories'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Down the Holler: A Reflection of Appalachian Culture and Folklore Through a Visual Lewis Carroll Rei'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -38094,7 +38094,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Yiran Qin</t>
+          <t>Yi Song</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -38126,7 +38126,7 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The World on Screen: Application of Motion Graphics in E-books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Hidden Clues and Visual Connections in Multi-Platform Children’s Stories'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -38134,7 +38134,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Emilie Seda</t>
+          <t>Jenna Talley</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -38166,7 +38166,7 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Illustration Pedagogy: How Teachers Employ Children's Books as a Pedagogical Tool to Improve Cogniti'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Effective Messaging Through Minimalism: The Power of Simplicity in Advertising'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
@@ -38174,7 +38174,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Yuxin Shang</t>
+          <t>Darihana Torres González</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -38206,7 +38206,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Enriching Book Cover Illustration with Different Materials'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Creation of The Settlers: Colonialism and Its Represention in Video Games'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
@@ -38214,7 +38214,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Audrey Song</t>
+          <t>Sijie Xiao</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -38246,7 +38246,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Beyond Drawing Nature, Science and Culture: The Fusion of the Artist's Personal Style and Scientific'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Art of Game Mechanics: From Digital Game Art to Strategic Tabletop Experiences'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
@@ -38254,7 +38254,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Paul V. Thompson</t>
+          <t>Tina Yan</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -38286,7 +38286,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Henny Penny and the Adult Picture Book Market'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'CD Cases: A Visual and Interactive Journey of Sound'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
@@ -38294,7 +38294,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AyaBird Wu</t>
+          <t>Hualei Zhao</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -38326,7 +38326,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'From the Perspective of Illustrators: Exploring Visual Narrative in Story Collection Adaptations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Emergence of Fictional Culture: Analysis of Concept Art &amp; Cross-Cultural Fusion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
@@ -38334,7 +38334,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Juntang Xu</t>
+          <t>Jiayin Cheng</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -38366,7 +38366,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Use of White Space in Picture Books  A Study of Aesthetics and Narrative'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Little Girl in Cockroach Kingdom: Narrative Strategies in Children’s Science Picture Books and the M'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -38374,7 +38374,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shiyao Yin</t>
+          <t>Yezi Dai</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -38406,7 +38406,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Exploring How Decorative Elements Support Visual Storytelling in Illustrated Book'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Things We Carry, Things We Eat: Visual Stories of Food, Culture, and Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
@@ -38414,7 +38414,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lingyan Zhang</t>
+          <t>Yinuo Fang</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -38446,7 +38446,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Beyond the Senses: Exploring the Interactions and Impact of Vision and Olfaction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Visual Narratives of the Fox Spirit: A Cross-Cultural Study of Chinese and Western Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -38454,7 +38454,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Yuanyuan Zhang</t>
+          <t>Tianning He</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -38486,7 +38486,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Hidden Palettes : Exploring the Fusion of Food and Urban Identity in China's Lesser-Known  Cities Th'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Atmosphere and Abstraction in Tarot Illustration: Expanding the Design Language of an Original Deck'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
@@ -38494,7 +38494,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kathleen Burns</t>
+          <t>Brooke Mackenzie Hoban</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -38526,7 +38526,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Everyday Ethnography: Illustrated Portraiture as Accessible Anthropology'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Symbiosis: An Analysis of How Environments and Environmentalism Make Creatures—Big and Small—Who The'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
@@ -38534,7 +38534,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yuchen Cui</t>
+          <t>David Hortta</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -38566,7 +38566,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Influence of Dynamic Lighting and Color in Video Games on Image Mood and Player Emotion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Visual Exploration of Religious Ideologies in Concept Art and Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
@@ -38574,7 +38574,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jake Steven Czubinski</t>
+          <t>Jake Damien-Moguel</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -38606,7 +38606,7 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Weyward Cove: Intersection of Cultural Identity and Queer Representation for Youth in Children's Tel'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Let the Audience Think'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
@@ -38614,7 +38614,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jesse A Reese</t>
+          <t>Susannah Klooster</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -38646,7 +38646,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Shadows of Fear: A Look at the Use of Fear in Illustration as a Drive for Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Making the Almost Extinct Commonplace: Increasing Ecological Awareness Through Surface Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
@@ -38654,7 +38654,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Amani Hoskin</t>
+          <t>Lauren Leibold</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -38686,7 +38686,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'From One 2 One: Twins and the Exploration of Media, Narrative and Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Picturing Grief: The Role Picture Books Play in Children's Lives'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J94" t="inlineStr"/>
@@ -38694,7 +38694,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Yangyu Li</t>
+          <t>Xiao Li</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -38726,7 +38726,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Storytelling Through Tactile Engagement: The Interactive Power of Artists’ Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Gouache Resist: Unpredictable and Random Texture Revealed Under Water Washing'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
@@ -38734,7 +38734,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>María Rosa Angélica Ramos Berríos</t>
+          <t>Xiaohui Liu</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -38766,7 +38766,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Through the Glass: The Art of Belonging Through Puerto Rican Folklore and Surface Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Cross-Cultural Visual Narratives in Picture Books: Representing Joy and Mourning in Global Hug'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -38774,7 +38774,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lauren Julianna Schermerhorn</t>
+          <t>Yue Li</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -38806,7 +38806,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Down the Holler: A Reflection of Appalachian Culture and Folklore Through a Visual Lewis Carroll Rei'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Seeing Sound: The Bridge Between Silence and Music'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -38814,7 +38814,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Yi Song</t>
+          <t>Minghan (Mandy) Zhang</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -38846,7 +38846,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Hidden Clues and Visual Connections in Multi-Platform Children’s Stories'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Solar Punk and The Power of Hope Within Imaginary Future'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -38854,7 +38854,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jenna Talley</t>
+          <t>Anosh Master</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -38886,7 +38886,7 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Effective Messaging Through Minimalism: The Power of Simplicity in Advertising'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Illustrations That Subvert Expectations Set by the Tropes and Trends of Digital Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -38894,7 +38894,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Darihana Torres González</t>
+          <t>Vedika Mehra</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -38926,7 +38926,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Creation of The Settlers: Colonialism and Its Represention in Video Games'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Bridging Gaps: The Role of Metaphor in Illustration for Communication and Connection'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -38934,7 +38934,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sijie Xiao</t>
+          <t>Veronica Morton</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -38966,7 +38966,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Art of Game Mechanics: From Digital Game Art to Strategic Tabletop Experiences'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Echoes of Once Upon a Time Two Reimagined Fairy Tale Story Pitches'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -38974,7 +38974,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tina Yan</t>
+          <t>Noah Martin Rivaz</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -39006,7 +39006,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'CD Cases: A Visual and Interactive Journey of Sound'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Redefining Adaptation of Myth Through Arthurian Legend'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -39014,7 +39014,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hualei Zhao</t>
+          <t>Maria del Socorro Patiño</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -39046,7 +39046,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Emergence of Fictional Culture: Analysis of Concept Art &amp; Cross-Cultural Fusion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Stories That Shape Children: The Power of Diverse Literacy in Education'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -39054,7 +39054,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jiayin Cheng</t>
+          <t>Gretchen Pickering</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -39086,7 +39086,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Little Girl in Cockroach Kingdom: Narrative Strategies in Children’s Science Picture Books and the M'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Sigrid and the Seagull City: From Children's Book to Immersive Experience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -39094,7 +39094,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Yezi Dai</t>
+          <t>Yang Qian</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -39126,7 +39126,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Things We Carry, Things We Eat: Visual Stories of Food, Culture, and Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'A Journey Around the World: Visual Storytelling of Cultural Diversity Through Children's Book Illust'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
@@ -39134,7 +39134,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Yinuo Fang</t>
+          <t>Ruikang Qin</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -39166,7 +39166,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Visual Narratives of the Fox Spirit: A Cross-Cultural Study of Chinese and Western Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Uplifting: The Modern Marketisation of Classical Literature Through Conceptual Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -39174,7 +39174,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Jordyn Goodman</t>
+          <t>Chiara Miraglia Renda</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -39206,7 +39206,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Cyber Girls: Bringing to Life STEAM Interests in Children Through Toy Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'We Will Never Be Silenced'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -39214,7 +39214,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tianning He</t>
+          <t>Natalie Cacioppo Sanders</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -39246,7 +39246,7 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Atmosphere and Abstraction in Tarot Illustration: Expanding the Design Language of an Original Deck'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Sword &amp; Seer: Visual Development, Stories, and Soul'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -39254,7 +39254,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Brooke Mackenzie Hoban</t>
+          <t>Feier Shen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -39286,7 +39286,7 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Symbiosis: An Analysis of How Environments and Environmentalism Make Creatures—Big and Small—Who The'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Fabric of Fiction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -39294,7 +39294,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>David Hortta</t>
+          <t>Yuanhao Tang</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -39326,7 +39326,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Visual Exploration of Religious Ideologies in Concept Art and Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Swords And Magic: Integrating Eastern Wuxia and Western Fantasy in Illustrated Adaptations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -39334,7 +39334,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jake Damien-Moguel</t>
+          <t>Leqi Wang</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -39366,7 +39366,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Let the Audience Think'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Visual Construction of Chinese Fantasy: Integrating Chinese Culture and Sci-Fi Elements'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -39374,7 +39374,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Susannah Klooster</t>
+          <t>Qi Wang</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -39406,7 +39406,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Making the Almost Extinct Commonplace: Increasing Ecological Awareness Through Surface Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'From Farm to Table: Enhancing Agricultural Product Marketing Through Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -39414,7 +39414,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lauren Leibold</t>
+          <t>Yuxin Wu</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -39446,7 +39446,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Picturing Grief: The Role Picture Books Play in Children's Lives'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Interactive Illustrations: Enriching Engagement in Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -39454,7 +39454,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Xiao Li</t>
+          <t>Xialin Qu</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -39486,7 +39486,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Gouache Resist: Unpredictable and Random Texture Revealed Under Water Washing'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'Designing an Interactive Picture Book for Children: Fostering Creativity Through Craft-Based Storyte'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -39494,7 +39494,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Xiaohui Liu</t>
+          <t>Yu Guo</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -39526,7 +39526,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Cross-Cultural Visual Narratives in Picture Books: Representing Joy and Mourning in Global Hug'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Painting/Drawing; thesis title 'The Unseen Pages of Single Childhood'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -39534,18 +39534,18 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Yue Li</t>
+          <t>NyLainah DeNee Brewer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Sculpture (SCAD)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -39566,7 +39566,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Seeing Sound: The Bridge Between Silence and Music'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Sculpture; thesis title 'Beyond The Freak Show: Sculpting Stories of Black Resilience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -39574,13 +39574,13 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Wynter Malone</t>
+          <t>Anna Noel Shackelford</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Sculpture (SCAD)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -39606,7 +39606,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Magnificent Moths: Representing the Beauty and Purpose of All in Nature'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Sculpture; thesis title 'Terms &amp; Conditions: The Privacy Paradox of the Uninformed Smartphone Consumer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -39614,13 +39614,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Minghan (Mandy) Zhang</t>
+          <t>Louisa Bristol</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Sculpture (SCAD)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -39646,7 +39646,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Solar Punk and The Power of Hope Within Imaginary Future'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Sculpture; thesis title 'Indecorous'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -39654,13 +39654,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Anosh Master</t>
+          <t>Olivia Esperanza Hill Esquivel</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Fibers (SCAD)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -39686,7 +39686,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Illustrations That Subvert Expectations Set by the Tropes and Trends of Digital Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fiber and Material Arts; thesis title 'The Form of Memory: How Textile Process and Theory Can Reveal the Mind'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -39694,13 +39694,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vedika Mehra</t>
+          <t>Rutuja Pawase</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Fibers (SCAD)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -39726,7 +39726,7 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Bridging Gaps: The Role of Metaphor in Illustration for Communication and Connection'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fiber and Material Arts; thesis title 'The Geometry of Making: Sacred Geometry as a Bridge Between Traditional Wisdom and Digital Innovatio'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -39734,13 +39734,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Veronica Morton</t>
+          <t>Malavika Singh Thakur</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Fibers (SCAD)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -39766,7 +39766,7 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Echoes of Once Upon a Time Two Reimagined Fairy Tale Story Pitches'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fiber and Material Arts; thesis title 'Chintz to Cheent: An Imagined Borderless World'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -39774,18 +39774,18 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Noah Martin Rivaz</t>
+          <t>Vince Andrew Lusk</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -39806,7 +39806,7 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Redefining Adaptation of Myth Through Arthurian Legend'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Aide-Memoire'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -39814,18 +39814,18 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maria del Socorro Patiño</t>
+          <t>Ziyi Yan</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -39846,7 +39846,7 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Stories That Shape Children: The Power of Diverse Literacy in Education'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Dreamscapes of Identity and Self Discovery in Photography'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -39854,18 +39854,18 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Gretchen Pickering</t>
+          <t>Calah Levy Burns</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -39886,7 +39886,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Sigrid and the Seagull City: From Children's Book to Immersive Experience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Roots &amp; Remnants'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -39894,13 +39894,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Hollie Puterbaugh</t>
+          <t>Nisha Pradeep</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -39926,7 +39926,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Layers of Meaning: Conceptual Devices in Contemporary Editorial Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'The Fold of Unfolding Motion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -39934,13 +39934,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Yang Qian</t>
+          <t>Jennifer E. Wilkosz</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -39966,7 +39966,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'A Journey Around the World: Visual Storytelling of Cultural Diversity Through Children's Book Illust'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Transcending the Blue: Touch, Look, and Wonder'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -39974,13 +39974,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ruikang Qin</t>
+          <t>Chen Zhao</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -40006,7 +40006,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Uplifting: The Modern Marketisation of Classical Literature Through Conceptual Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'WildArtifice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -40014,13 +40014,13 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Chiara Miraglia Renda</t>
+          <t>Katherine Barbieri</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -40046,7 +40046,7 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'We Will Never Be Silenced'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Nobody's Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -40054,13 +40054,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Natalie Cacioppo Sanders</t>
+          <t>Dona Cecile Bilyeu-Dittman</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -40086,7 +40086,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Sword &amp; Seer: Visual Development, Stories, and Soul'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Ephemeral Beauty and Social Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -40094,13 +40094,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Feier Shen</t>
+          <t>Dante Fewster Holdsworth</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -40126,7 +40126,7 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Fabric of Fiction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'If I Ruled the World'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -40134,13 +40134,13 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Maggie Stinauer</t>
+          <t>Hannah Elizabeth Martin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -40166,7 +40166,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Story Telling: The Role of Conceptual Illustration in Society, and the Editorial Outlet'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'A Visit Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -40174,13 +40174,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lai Wei</t>
+          <t>Lian Perez</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -40206,7 +40206,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Symbols in Illustration &amp; How They Affect Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'La Luz Que Me Guia'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -40214,13 +40214,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Yuanhao Tang</t>
+          <t>Etoia Rivera</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -40246,7 +40246,7 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Swords And Magic: Integrating Eastern Wuxia and Western Fantasy in Illustrated Adaptations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Biotic Crisis: The 6th Extinction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -40254,13 +40254,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Leqi Wang</t>
+          <t>Jordan Michael Patterson</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -40286,7 +40286,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Visual Construction of Chinese Fantasy: Integrating Chinese Culture and Sci-Fi Elements'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'To Look Without Fear: Exploring Trauma &amp; Transformation Through Art'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -40294,13 +40294,13 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Qi Wang</t>
+          <t>Emma Varland</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -40326,7 +40326,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'From Farm to Table: Enhancing Agricultural Product Marketing Through Illustration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Light Touches'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -40334,13 +40334,13 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Yuxin Wu</t>
+          <t>Daniel Brevick</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -40366,7 +40366,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Interactive Illustrations: Enriching Engagement in Picture Books'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Realism Reframed: Creating the Illusion of Reality with Photography'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -40374,13 +40374,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Xialin Qu</t>
+          <t>Parrish Hargraves</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -40406,7 +40406,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Designing an Interactive Picture Book for Children: Fostering Creativity Through Craft-Based Storyte'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'This Body, This Want'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -40414,13 +40414,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jiayi Zhang</t>
+          <t>Jingjing Lyu</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -40446,7 +40446,7 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Influence of Line Drawing in the Song Dynasty to Present Illustration Creation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Body and Being'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -40454,13 +40454,13 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Yu Guo</t>
+          <t>Tori Piscitelli</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -40486,7 +40486,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'The Unseen Pages of Single Childhood'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'All Within Time'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -40494,13 +40494,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Richard Zhao</t>
+          <t>Ziqiao Huang</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Illustration (SCAD)</t>
+          <t>Photography (SCAD)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -40526,7 +40526,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Medium: Painting/Drawing; thesis title 'Cognition: Exploration of Character Archetypes and Symbolism Through the Lens of Environmental Desig'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Photography; thesis title 'Lost in Translation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
@@ -40534,13 +40534,13 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NyLainah DeNee Brewer</t>
+          <t>Xiang Li</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sculpture (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -40566,7 +40566,7 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Medium: Sculpture; thesis title 'Beyond The Freak Show: Sculpting Stories of Black Resilience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Spatial Storytelling in Stylized Worlds : A Digital Study of Stop-Motion Animation Aesthetics'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -40574,18 +40574,18 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Anna Noel Shackelford</t>
+          <t>Amanda Maria Payne</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sculpture (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -40606,7 +40606,7 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Medium: Sculpture; thesis title 'Terms &amp; Conditions: The Privacy Paradox of the Uninformed Smartphone Consumer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Thaumaturgical : Rigging and Environmental Storytelling in 3D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -40614,18 +40614,18 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Emma Adler</t>
+          <t>Yihan Wang</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sculpture (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -40646,7 +40646,7 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Medium: Sculpture; thesis title 'AMI: The Digital Representation of Women in Western Pop Culture'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Mumei : A Story About Loneliness'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
@@ -40654,18 +40654,18 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Louisa Bristol</t>
+          <t>Neko Pilarcik-Tellez</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sculpture (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -40686,7 +40686,7 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Medium: Sculpture; thesis title 'Indecorous'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Cel Shading via Compositing for 2D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -40694,18 +40694,18 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Olivia Esperanza Hill Esquivel</t>
+          <t>Xuan (Ruth) Zhang</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fibers (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -40726,7 +40726,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Medium: Fiber and Material Arts; thesis title 'The Form of Memory: How Textile Process and Theory Can Reveal the Mind'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Scaling Craftsmanship : The Role of AI Assistance in Modern Animation Production'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
@@ -40734,18 +40734,18 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lusiana Morales Febo</t>
+          <t>Miles Zhang</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fibers (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -40766,7 +40766,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Medium: Fiber and Material Arts; thesis title 'Earthtanglements: Reconnecting and Renewing Relationships with Our Environment'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of Error 404 : Character Animation In The Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
@@ -40774,18 +40774,18 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Rutuja Pawase</t>
+          <t>Momo Chang</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Fibers (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -40806,7 +40806,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Medium: Fiber and Material Arts; thesis title 'The Geometry of Making: Sacred Geometry as a Bridge Between Traditional Wisdom and Digital Innovatio'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of Sculpted'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
@@ -40814,18 +40814,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Malavika Singh Thakur</t>
+          <t>Xinyu Chen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Fibers (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -40846,7 +40846,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Medium: Fiber and Material Arts; thesis title 'Chintz to Cheent: An Imagined Borderless World'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Neighbors : Exploring Wall-bound Interaction and Character Contrast in a UPA-Inspired 2D Animated Co'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -40854,13 +40854,13 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Vince Andrew Lusk</t>
+          <t>Qingtian Deng</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -40886,7 +40886,7 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Aide-Memoire'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Creation of Fight for the Fish : A Study on the Effect of Using Character Animation/Special Effe'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
@@ -40894,13 +40894,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ziyi Yan</t>
+          <t>Menglei Du</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -40926,7 +40926,7 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Dreamscapes of Identity and Self Discovery in Photography'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Application of Exaggerated Rigging Techniques to Support Cartoony Character Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -40934,13 +40934,13 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Melanee "Mel" Brown</t>
+          <t>Jiyu Zhao</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -40966,7 +40966,7 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Burney Road'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Home : Using of First-Person Point of View in Animation Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
@@ -40974,13 +40974,13 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Calah Levy Burns</t>
+          <t>Merit Chandler Huggins</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -41006,7 +41006,7 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Roots &amp; Remnants'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Zone'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -41014,13 +41014,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Kourtney Iman King</t>
+          <t>Yingzhi Hu</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -41046,7 +41046,7 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Soulaan Femme'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Finding Color : The Making of "The Lost"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
@@ -41054,13 +41054,13 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Nisha Pradeep</t>
+          <t>Michael Mauro</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -41086,7 +41086,7 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'The Fold of Unfolding Motion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Shroud Falls'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
@@ -41094,13 +41094,13 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Jennifer E. Wilkosz</t>
+          <t>Yue Peng</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -41126,7 +41126,7 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Transcending the Blue: Touch, Look, and Wonder'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Exploring Character Look Development : A Case Study on Characters in Meowrry Christmas'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
@@ -41134,13 +41134,13 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Chen Zhao</t>
+          <t>Yilin Zhao</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -41166,7 +41166,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'WildArtifice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Meowrry Christmas : Exploring Stylized 3D Environment Design for Visual Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
@@ -41174,13 +41174,13 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Katherine Barbieri</t>
+          <t>Kaite Zhang</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -41206,7 +41206,7 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Nobody's Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Sunset Desert'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
@@ -41214,13 +41214,13 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dona Cecile Bilyeu-Dittman</t>
+          <t>Shuchao Ding</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -41246,7 +41246,7 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Ephemeral Beauty and Social Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Parallel Cutting and Narrative Deception : Constructing Misleading Timelines in Animation through St'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
@@ -41254,13 +41254,13 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Taylor Edgerton</t>
+          <t>Jiaji Ma</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -41286,7 +41286,7 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Book Under the Pew'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Survival Instinct in the Apocalypse : How Armor Can Convey and Enhance a Story Through Communicating'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
@@ -41294,13 +41294,13 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dante Fewster Holdsworth</t>
+          <t>Yijia Ye</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -41326,7 +41326,7 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'If I Ruled the World'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Going Back Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -41334,13 +41334,13 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Hailey R. Kasper</t>
+          <t>Kangwen Shi</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -41366,7 +41366,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Anything Magazine'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Utilizing Chekhov's Gun as a Narrative Principle : Exploring the Humoristic Spirit in the World of A'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
@@ -41374,13 +41374,13 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hannah Elizabeth Martin</t>
+          <t>Aditya H. Napanda</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -41406,7 +41406,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'A Visit Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Bird's Eye : Experimental Animation Using 3D Zoetropes'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -41414,13 +41414,13 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lian Perez</t>
+          <t>Xiaoxi Zhang</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -41446,7 +41446,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'La Luz Que Me Guia'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Combination of Motion Capture and Keyframed Animation Techniques in 3D Character Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -41454,13 +41454,13 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Etoia Rivera</t>
+          <t>Jiaxing Yang</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -41486,7 +41486,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Biotic Crisis: The 6th Extinction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'A Study of Unorthodox Lighting Techniques in 3D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J164" t="inlineStr"/>
@@ -41494,13 +41494,13 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Xavier Thompson</t>
+          <t>PeiLing Chen</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -41526,7 +41526,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'A Place Beyond the Pine'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Utilizing the Success of American Fables in Animation to Create Chinese Proverb Animations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
@@ -41534,13 +41534,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Jordan Michael Patterson</t>
+          <t>Ziyu Zhen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -41566,7 +41566,7 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'To Look Without Fear: Exploring Trauma &amp; Transformation Through Art'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'A Tap Water Dream : Environmental Storytelling in First Person Perspective Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -41574,13 +41574,13 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Emma Varland</t>
+          <t>Shuxian Chen</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -41606,7 +41606,7 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Light Touches'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Find It : Ecological Truth-Seeking in a 2D Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
@@ -41614,13 +41614,13 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Daniel Brevick</t>
+          <t>Jessica Ambadipudi</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -41646,7 +41646,7 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Realism Reframed: Creating the Illusion of Reality with Photography'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Highway 81 : Exploring How Minimal Anthropomorphism Enhances Self-Identification by Transcending Age'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
@@ -41654,13 +41654,13 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Parrish Hargraves</t>
+          <t>Cobra Yu</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -41686,7 +41686,7 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'This Body, This Want'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Creation of 'Silent Scream' : Visual Rhetoric in CG War-Themed Action and Anti-War Narrative'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
@@ -41694,13 +41694,13 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Jingjing Lyu</t>
+          <t>Ziyi Xu</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -41726,7 +41726,7 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Body and Being'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Lost : Visual Metaphors in Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -41734,13 +41734,13 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tori Piscitelli</t>
+          <t>Yezheng Sheng</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -41766,7 +41766,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'All Within Time'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Falling : Into a Dream of Poetic Imagery'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
@@ -41774,13 +41774,13 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DeAngelo Williams</t>
+          <t>Angel Harris</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -41806,7 +41806,7 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Connections'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Integration of 2D Animation into 3D Backgrounds in 'The Awakener''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
@@ -41814,13 +41814,13 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Zhiquan Zhao</t>
+          <t>Tianjiao Dong</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -41846,7 +41846,7 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Journey to the American Dream'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Between the Line: Audio-visual Representation of Sensory Anxiety'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J173" t="inlineStr"/>
@@ -41854,13 +41854,13 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ziqiao Huang</t>
+          <t>Jiayi Gu</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Photography (SCAD)</t>
+          <t>Animation (SCAD)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -41886,7 +41886,7 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Medium: Photography; thesis title 'Lost in Translation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Lotus Scroll : Study of the Pipeline for Creating an Unreal Engine Game That Focuses on Animated'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J174" t="inlineStr"/>
@@ -41894,7 +41894,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Xiang Li</t>
+          <t>Fei Gai</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -41905,7 +41905,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -41926,7 +41926,7 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Spatial Storytelling in Stylized Worlds : A Digital Study of Stop-Motion Animation Aesthetics'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of 'The Awakener''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
@@ -41934,7 +41934,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Lan Luo</t>
+          <t>Soumya Deshpande</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -41945,7 +41945,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -41966,7 +41966,7 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Unknown Waiting : The Use of Visual Metaphor in 3D Animated Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Exploring the Impact of Algorithmic and Intrusive Advertising Through Storytelling in Live Action an'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J176" t="inlineStr"/>
@@ -41974,7 +41974,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Amanda Maria Payne</t>
+          <t>Yuyao Cong</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -41985,7 +41985,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -42006,7 +42006,7 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Thaumaturgical : Rigging and Environmental Storytelling in 3D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Animation as Language and the Potential of Abstraction in 2D Animation Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J177" t="inlineStr"/>
@@ -42014,7 +42014,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sarah Via</t>
+          <t>Weitao Dai</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -42025,7 +42025,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -42046,7 +42046,7 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Ranger Dave Enjoys a Quiet Evening : A Study in the Real and Unreal in Animated Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Memories of My Offices'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J178" t="inlineStr"/>
@@ -42054,7 +42054,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Yihan Wang</t>
+          <t>Elijah Conway</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -42065,7 +42065,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -42086,7 +42086,7 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Mumei : A Story About Loneliness'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Moving On : A Short 2D Film on Guilt'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J179" t="inlineStr"/>
@@ -42094,7 +42094,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Yoona Hwang</t>
+          <t>Luke Vincent DeSimone</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -42105,7 +42105,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -42126,7 +42126,7 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Silence : Visualizing Sound through Hybrid Animation for Disability Advocacy and Inclusion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'A Long Shot : Finding a Future in Sports Through Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J180" t="inlineStr"/>
@@ -42134,7 +42134,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Neko Pilarcik-Tellez</t>
+          <t>Janhavi Parekh</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -42145,7 +42145,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -42166,7 +42166,7 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Cel Shading via Compositing for 2D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'From Setting to Character : Applying Character Arcs to Environments in Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J181" t="inlineStr"/>
@@ -42174,7 +42174,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Xuan (Ruth) Zhang</t>
+          <t>Guanwen Wang</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -42185,7 +42185,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -42206,7 +42206,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Scaling Craftsmanship : The Role of AI Assistance in Modern Animation Production'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Visualizing Psychological Isolation through Stylized 3D Animation in Deep Space'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
@@ -42214,7 +42214,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Miles Zhang</t>
+          <t>Rohit Pant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -42225,7 +42225,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -42246,7 +42246,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of Error 404 : Character Animation In The Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Silent Comfort'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -42254,7 +42254,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Momo Chang</t>
+          <t>Sriya Reddy Nallannagari</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -42265,7 +42265,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -42286,7 +42286,7 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of Sculpted'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Evolution of Time through Environmental Storytelling Using Limited Character Representation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -42294,7 +42294,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Xinyu Chen</t>
+          <t>Yingyan Lin</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -42326,7 +42326,7 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Neighbors : Exploring Wall-bound Interaction and Character Contrast in a UPA-Inspired 2D Animated Co'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Back to Work'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -42334,7 +42334,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Qingtian Deng</t>
+          <t>Lening Xu</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -42345,7 +42345,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -42366,7 +42366,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Creation of Fight for the Fish : A Study on the Effect of Using Character Animation/Special Effe'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of The Heist'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -42374,7 +42374,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Menglei Du</t>
+          <t>Ryan Cuscaden</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -42385,7 +42385,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -42406,7 +42406,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Application of Exaggerated Rigging Techniques to Support Cartoony Character Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Ballad of Skittle Jacks : A Discovery of Story Through Narrative Sculpture'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -42414,7 +42414,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jiyu Zhao</t>
+          <t>Mira Taliaferro</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -42425,7 +42425,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -42446,7 +42446,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Home : Using of First-Person Point of View in Animation Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Making of Siren : Exploring Trauma and Healing Through Stop-Motion Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -42454,7 +42454,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Merit Chandler Huggins</t>
+          <t>Haotian Zou</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -42465,7 +42465,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -42486,7 +42486,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Zone'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Lime'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -42494,7 +42494,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Yingzhi Hu</t>
+          <t>Yuqi Wang</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -42526,7 +42526,7 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Finding Color : The Making of "The Lost"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Travel Sketchbook'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -42534,7 +42534,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Gabby Gillespie</t>
+          <t>Geoffrey Aaron Asch</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -42566,7 +42566,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'How the Animal Animated Film Recontextualizes Our Perception of History'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Making of Footprints'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -42574,7 +42574,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Michael Mauro</t>
+          <t>Linhan Chen</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -42606,7 +42606,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Shroud Falls'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! An Exploration of 3D Digital Tools to Create a Hand-Crafted Stop-Motion Aesthetic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -42614,7 +42614,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Yue Peng</t>
+          <t>Ruoyu Liu</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -42646,7 +42646,7 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Exploring Character Look Development : A Case Study on Characters in Meowrry Christmas'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! : Between Clay and Code: Crafting Stop-Motion Aesthetic in 3D'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -42654,7 +42654,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Yilin Zhao</t>
+          <t>Yimin Sun</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -42686,7 +42686,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Meowrry Christmas : Exploring Stylized 3D Environment Design for Visual Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! : Crafting Fun through Cartoon Aesthetics and Stop-Motion Innovation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -42694,7 +42694,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Kaite Zhang</t>
+          <t>Jonathan Po-Han Hsieh</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -42726,7 +42726,7 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Sunset Desert'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Ducky : Ambiguous Friendship Narratives in the Animated Short Film Format'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -42734,7 +42734,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Shuchao Ding</t>
+          <t>Yaejin Esther Son</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -42766,7 +42766,7 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Parallel Cutting and Narrative Deception : Constructing Misleading Timelines in Animation through St'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Sunburn'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -42774,7 +42774,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Jiaji Ma</t>
+          <t>Indi L. Solis</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -42806,7 +42806,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Survival Instinct in the Apocalypse : How Armor Can Convey and Enhance a Story Through Communicating'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Pixel World : Developing Pixel Art as an Effective Storytelling Mechanism for the Animated Film Indu'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -42814,7 +42814,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Yijia Ye</t>
+          <t>Emily Ann Stong</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -42846,7 +42846,7 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Going Back Home'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Cat-Astrophe : A Deeper Look into the POV of a Cat's Mind and Its Relation to Quadruped Animation an'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -42854,7 +42854,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Kangwen Shi</t>
+          <t>Mian Brindisi</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -42886,7 +42886,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Utilizing Chekhov's Gun as a Narrative Principle : Exploring the Humoristic Spirit in the World of A'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Process of "Dragon in Training" : Utilizing Unreal Engine 5 to Create a 3D Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -42894,7 +42894,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Aditya H. Napanda</t>
+          <t>Aaron Raven Campilan</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -42926,7 +42926,7 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Bird's Eye : Experimental Animation Using 3D Zoetropes'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Magic in the Horror : Exploring the Intersection of Lovecraftian Horror and Magical Realism'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -42934,7 +42934,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Xiaoxi Zhang</t>
+          <t>Avanthi Vijay Kamat</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -42966,7 +42966,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Combination of Motion Capture and Keyframed Animation Techniques in 3D Character Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Predictive Power of Environmental Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -42974,7 +42974,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Jiaxing Yang</t>
+          <t>Zhubingjie Ye</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -43006,7 +43006,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'A Study of Unorthodox Lighting Techniques in 3D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Beyond My Screen : Remember to Stop and Smell the Roses'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -43014,7 +43014,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PeiLing Chen</t>
+          <t>Choc Xuechen Yang</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -43046,7 +43046,7 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Utilizing the Success of American Fables in Animation to Create Chinese Proverb Animations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'The Art of Draguardia : Exploration of Cinematic Teaser Trailer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -43054,7 +43054,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ziyu Zhen</t>
+          <t>Qianqian Zhang</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -43086,7 +43086,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'A Tap Water Dream : Environmental Storytelling in First Person Perspective Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Play Again?'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -43094,7 +43094,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Shuxian Chen</t>
+          <t>Lyndon Fan</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -43126,7 +43126,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Find It : Ecological Truth-Seeking in a 2D Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: 2D/3D Animation; thesis title 'Aesthetics Through Rigging : Supporting and Enabling Stylistic Choices Through Character Setup'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
@@ -43134,18 +43134,18 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Jessica Ambadipudi</t>
+          <t>Rachel Shipman</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -43166,7 +43166,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Highway 81 : Exploring How Minimal Anthropomorphism Enhances Self-Identification by Transcending Age'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'How 'Buffy the Vampire Slayer' Shaped Sapphic Representation in Broadcast Television'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -43174,18 +43174,18 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Freddy Bendekgey</t>
+          <t>Elijah Willis</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -43206,7 +43206,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Queer-Coded Lighting : How Lighting and Cinematography Can Subvert the Expectations of the Male Gaze'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Amethyst Reign'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
@@ -43214,18 +43214,18 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Cobra Yu</t>
+          <t>Lauryn Alexandria Terry</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -43246,7 +43246,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Creation of 'Silent Scream' : Visual Rhetoric in CG War-Themed Action and Anti-War Narrative'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
@@ -43254,18 +43254,18 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Daniela Rumbaut</t>
+          <t>Roni Lovejoy</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -43286,7 +43286,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Chopin et Liszt : Hand-Painted Watercolor Textures for 3D Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
@@ -43294,18 +43294,18 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ziyi Xu</t>
+          <t>Zyria Jessie</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -43326,7 +43326,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Lost : Visual Metaphors in Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -43334,18 +43334,18 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Yezheng Sheng</t>
+          <t>Arielle Engle</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -43366,7 +43366,7 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Falling : Into a Dream of Poetic Imagery'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'It Creeps'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -43374,18 +43374,18 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Drew Clark</t>
+          <t>Taoran Liu</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -43406,7 +43406,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Cure Haven Introduction'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Little Puppy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
@@ -43414,18 +43414,18 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Angel Harris</t>
+          <t>Michael Jones</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -43446,7 +43446,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Integration of 2D Animation into 3D Backgrounds in 'The Awakener''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'By My Side'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J213" t="inlineStr"/>
@@ -43454,18 +43454,18 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Tianjiao Dong</t>
+          <t>Bixuan Zhang</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -43486,7 +43486,7 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Between the Line: Audio-visual Representation of Sensory Anxiety'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Little Puppy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
@@ -43494,18 +43494,18 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Jiayi Gu</t>
+          <t>Ziqin Ma</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -43526,7 +43526,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Lotus Scroll : Study of the Pipeline for Creating an Unreal Engine Game That Focuses on Animated'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Lighting the Look : How LED Color Control Changed Cinematographic Style'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
@@ -43534,18 +43534,18 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Fei Gai</t>
+          <t>Niranjana Karumampuram Arunkumar</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -43566,7 +43566,7 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of 'The Awakener''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'What Girls Want'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
@@ -43574,18 +43574,18 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Soumya Deshpande</t>
+          <t>Regan Hutton</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -43606,7 +43606,7 @@
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Exploring the Impact of Algorithmic and Intrusive Advertising Through Storytelling in Live Action an'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'What Remains of Romance? : Cinema Taught Us How to Date'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
@@ -43614,18 +43614,18 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Yuyao Cong</t>
+          <t>Beatrise Ziedina</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -43646,7 +43646,7 @@
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Animation as Language and the Potential of Abstraction in 2D Animation Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Tongue Tied'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -43654,18 +43654,18 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Weitao Dai</t>
+          <t>Yuxi Zhang</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -43686,7 +43686,7 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Memories of My Offices'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Invisible Wounds : Institutional Trauma and Self-Redemption Faced by Women with Unplanned Pregnancy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J219" t="inlineStr"/>
@@ -43694,13 +43694,13 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Elijah Conway</t>
+          <t>Zhanlan Lei</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43726,7 +43726,7 @@
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Moving On : A Short 2D Film on Guilt'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Films Enhance Animal Emotional Expression Beyond Reality'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J220" t="inlineStr"/>
@@ -43734,13 +43734,13 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Luke Vincent DeSimone</t>
+          <t>Marina Kathy Saji</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43766,7 +43766,7 @@
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'A Long Shot : Finding a Future in Sports Through Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Impact of Interpretative Flashbacks on Narrative Complexity in Indian Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
@@ -43774,13 +43774,13 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Janhavi Parekh</t>
+          <t>C.J. Staidum</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -43806,7 +43806,7 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'From Setting to Character : Applying Character Arcs to Environments in Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Italian Neorealism : Where It Originated and The Connection It Has with Modern Day Documentary Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
@@ -43814,13 +43814,13 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Guanwen Wang</t>
+          <t>WeiChung Chen</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -43846,7 +43846,7 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Visualizing Psychological Isolation through Stylized 3D Animation in Deep Space'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Designing and Executing Exterior Day for Night Scenes on a Micro-budget Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
@@ -43854,13 +43854,13 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Rohit Pant</t>
+          <t>Alec Dixon</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -43886,7 +43886,7 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Silent Comfort'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Cutting to Glory : Editing Strategies in Sports Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J224" t="inlineStr"/>
@@ -43894,13 +43894,13 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sriya Reddy Nallannagari</t>
+          <t>Denise Francis Gordon</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -43926,7 +43926,7 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Evolution of Time through Environmental Storytelling Using Limited Character Representation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Tyler Perry's Studios : A Modern Take on Vertical Integration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J225" t="inlineStr"/>
@@ -43934,13 +43934,13 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Anindita Maturi</t>
+          <t>Brennan Haley</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -43966,7 +43966,7 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Mamidi : The Fusion of 2D and 3D Animation to Enhance Storytelling and Aesthetic Appeal'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Exposing the Repressed : The Horror of the Uncanny in Science Fiction Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -43974,13 +43974,13 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Iman Gadalla</t>
+          <t>Andrew James Taylor</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -44006,7 +44006,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Animation as Therapy : The Power of Character Design and Narrative Art in Art Therapy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'The Art of the Spoof : One of Comedy's Most Challenging Acts to Accomplish in American Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -44014,13 +44014,13 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Yingyan Lin</t>
+          <t>Sarabi Woods</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -44046,7 +44046,7 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Back to Work'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'The Push for Positive Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -44054,13 +44054,13 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Lening Xu</t>
+          <t>Yuheng Zhang</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -44086,7 +44086,7 @@
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Process Book of The Heist'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Duo'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -44094,13 +44094,13 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Ryan Cuscaden</t>
+          <t>Vusumuzi Mthembu</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -44126,7 +44126,7 @@
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Ballad of Skittle Jacks : A Discovery of Story Through Narrative Sculpture'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Gaze : The Decolonizing of the Black, Queer Self'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J230" t="inlineStr"/>
@@ -44134,13 +44134,13 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Mira Taliaferro</t>
+          <t>Shakira Murphy</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -44166,7 +44166,7 @@
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Making of Siren : Exploring Trauma and Healing Through Stop-Motion Animation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Fostered Deception'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J231" t="inlineStr"/>
@@ -44174,13 +44174,13 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Haotian Zou</t>
+          <t>Brandon Walker</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -44206,7 +44206,7 @@
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Lime'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Mindbound'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
@@ -44214,13 +44214,13 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Yuqi Wang</t>
+          <t>Chi Fan</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -44246,7 +44246,7 @@
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Travel Sketchbook'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Reimagining Intelligence : A Comparative Study of AI Representation in Contemporary Chinese and Amer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -44254,13 +44254,13 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Geoffrey Aaron Asch</t>
+          <t>Stephen Ford</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -44286,7 +44286,7 @@
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Making of Footprints'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Blood Upon Them'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J234" t="inlineStr"/>
@@ -44294,13 +44294,13 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Linhan Chen</t>
+          <t>Annie Funderburk</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -44326,7 +44326,7 @@
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! An Exploration of 3D Digital Tools to Create a Hand-Crafted Stop-Motion Aesthetic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Death's A Drag'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -44334,13 +44334,13 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Ruoyu Liu</t>
+          <t>Xinzhu Liu</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -44366,7 +44366,7 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! : Between Clay and Code: Crafting Stop-Motion Aesthetic in 3D'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'How Nonlinear Narrative Editing Shapes Characters' Inner Worlds and Emotional Resonance within Visua'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -44374,13 +44374,13 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Yimin Sun</t>
+          <t>R.J. Easy</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -44406,7 +44406,7 @@
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Claws? Chaos! : Crafting Fun through Cartoon Aesthetics and Stop-Motion Innovation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Love Me!'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -44414,13 +44414,13 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Mark J. Boone</t>
+          <t>Zhaoning Lyu</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -44446,7 +44446,7 @@
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Dog Eat Dogma : Expressing the Parallels of Man and Canine Stereotyping Through Anthropomorphism'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Behind the Animal Act : The Making of Emotional Illusions in Pet Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -44454,13 +44454,13 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Jonathan Po-Han Hsieh</t>
+          <t>Yili Ma</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -44486,7 +44486,7 @@
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Ducky : Ambiguous Friendship Narratives in the Animated Short Film Format'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Love Me!'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -44494,13 +44494,13 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Yaejin Esther Son</t>
+          <t>Hanzhong Bai</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -44526,7 +44526,7 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Sunburn'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'A Time to Wither : The Convergence of Aging and Slow Cinema in Contemporary Film Practice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J240" t="inlineStr"/>
@@ -44534,13 +44534,13 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ian Anastas</t>
+          <t>Shihao Fu</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -44566,7 +44566,7 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'ConTempt Warning : Cartoony Comedic Musical Performance in the Context of Contemporary Social Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Reincarnated Fear and the Unconscious : Symbolic Representations of Time and Identity in Cinema and'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -44574,13 +44574,13 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Indi L. Solis</t>
+          <t>Ziyou Li</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -44606,7 +44606,7 @@
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Pixel World : Developing Pixel Art as an Effective Storytelling Mechanism for the Animated Film Indu'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'How Cinematography Presents the Conflict between Gender Orientation and Family Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
@@ -44614,13 +44614,13 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Emily Ann Stong</t>
+          <t>Jiaxin Li</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -44646,7 +44646,7 @@
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Cat-Astrophe : A Deeper Look into the POV of a Cat's Mind and Its Relation to Quadruped Animation an'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'The Artificial Identity : The Political Philosophy of Cyborg Bodies and Identity/Soul in Science Fic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -44654,13 +44654,13 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Mian Brindisi</t>
+          <t>Eunique Foreman</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -44686,7 +44686,7 @@
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Process of "Dragon in Training" : Utilizing Unreal Engine 5 to Create a 3D Animated Short Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Sole Obsession'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -44694,13 +44694,13 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Aaron Raven Campilan</t>
+          <t>Jacob McKee</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -44726,7 +44726,7 @@
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Magic in the Horror : Exploring the Intersection of Lovecraftian Horror and Magical Realism'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'The Gay's Afoot : The Conceptualization and Making of 'My Dear Watson''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J245" t="inlineStr"/>
@@ -44734,13 +44734,13 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Avanthi Vijay Kamat</t>
+          <t>Garrison Rolle</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -44766,7 +44766,7 @@
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Predictive Power of Environmental Storytelling'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Colony'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
@@ -44774,13 +44774,13 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Zhubingjie Ye</t>
+          <t>Zitong Shu</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -44806,7 +44806,7 @@
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Beyond My Screen : Remember to Stop and Smell the Roses'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Time Fragments : Exploring the Emotional Resonance of Nonlinear Narrative'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J247" t="inlineStr"/>
@@ -44814,13 +44814,13 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Choc Xuechen Yang</t>
+          <t>Damian James Standen</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -44846,7 +44846,7 @@
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'The Art of Draguardia : Exploration of Cinematic Teaser Trailer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Dogs &amp; Drunks : Representations of Canines and Alcoholics from the Silent Era to the Modern Day'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -44854,13 +44854,13 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Qianqian Zhang</t>
+          <t>Ronesha Strickland</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -44886,7 +44886,7 @@
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Play Again?'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Beneath The Surface'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -44894,13 +44894,13 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Lyndon Fan</t>
+          <t>Christopher Williams</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Animation (SCAD)</t>
+          <t>Film &amp; Television (SCAD)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -44926,7 +44926,7 @@
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Medium: 2D/3D Animation; thesis title 'Aesthetics Through Rigging : Supporting and Enabling Stylistic Choices Through Character Setup'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Beneath The Surface'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -44934,7 +44934,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Rachel Shipman</t>
+          <t>Haolan Liu</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -44945,7 +44945,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -44966,7 +44966,7 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'How 'Buffy the Vampire Slayer' Shaped Sapphic Representation in Broadcast Television'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Captured Shadows : Self-Reflexivity and Masculine Duality in Neon-Noir'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J251" t="inlineStr"/>
@@ -44974,7 +44974,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Elijah Willis</t>
+          <t>Ivi D'vynne Wicks</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -44985,7 +44985,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -45006,7 +45006,7 @@
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Amethyst Reign'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'If You Got It : The Making of the Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J252" t="inlineStr"/>
@@ -45014,7 +45014,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Zilyu Ye</t>
+          <t>Serenity M. Kelly</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -45025,7 +45025,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -45046,7 +45046,7 @@
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Medium as Mirror : Investigating the Alignment of Reflexive Intent and Film Ontology in Independent'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'NO! Progression'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -45054,7 +45054,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Lauryn Alexandria Terry</t>
+          <t>Xinran Gu</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -45065,7 +45065,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -45086,7 +45086,7 @@
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Love, Tears, and Choice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -45094,7 +45094,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Roni Lovejoy</t>
+          <t>Alli Bargelski</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -45105,7 +45105,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -45126,7 +45126,7 @@
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Kitty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -45134,7 +45134,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Zyria Jessie</t>
+          <t>Emily Carvalheiro</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -45145,7 +45145,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -45166,7 +45166,7 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Guilty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Kitty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -45174,7 +45174,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Arielle Engle</t>
+          <t>Yeting Wang</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -45185,7 +45185,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -45206,7 +45206,7 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'It Creeps'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Filmmaking; thesis title 'Visual Storytelling Across Culture : Cinematography and Light in "Flight"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -45214,13 +45214,13 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Taoran Liu</t>
+          <t>Caroline Constantin Fogg</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -45246,7 +45246,7 @@
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Little Puppy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Graphic Design in Nation Building, Nationalism, and Community'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J258" t="inlineStr"/>
@@ -45254,13 +45254,13 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Michael Jones</t>
+          <t>Yuhan Feng</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -45286,7 +45286,7 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'By My Side'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Designing Silence: Rethinking Sexual Education in Contemporary China'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J259" t="inlineStr"/>
@@ -45294,13 +45294,13 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Bixuan Zhang</t>
+          <t>Jieun Kim</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -45326,7 +45326,7 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Little Puppy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Beyond Death: Digital Legacy, Mourning, and Posthumous Curation in the Digital Age'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J260" t="inlineStr"/>
@@ -45334,13 +45334,13 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Sean Malady</t>
+          <t>Ruoxi Liu</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -45366,7 +45366,7 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'The Advancements and New Techniques in Low-Light Digital Cinematography'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Redefining Success Narratives: How Visual Design Challenges Social Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J261" t="inlineStr"/>
@@ -45374,13 +45374,13 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Ziqin Ma</t>
+          <t>Shivali Meenakshi Murali</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -45406,7 +45406,7 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Lighting the Look : How LED Color Control Changed Cinematographic Style'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Beyond Vision'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J262" t="inlineStr"/>
@@ -45414,13 +45414,13 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Adrianna Amy-Delgado</t>
+          <t>Foster Whitney</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -45446,7 +45446,7 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Coming of Rage'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The Luxury Commodification of Cannabis'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J263" t="inlineStr"/>
@@ -45454,18 +45454,18 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Niranjana Karumampuram Arunkumar</t>
+          <t>Yinxuan Duan</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -45486,7 +45486,7 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'What Girls Want'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Raising Awareness Through Inclusive Graphic Design to Help Prevent Hearing Loss'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J264" t="inlineStr"/>
@@ -45494,18 +45494,18 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Regan Hutton</t>
+          <t>Junyuan Lan</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -45526,7 +45526,7 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'What Remains of Romance? : Cinema Taught Us How to Date'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Veiled Resistance in the Age of Unconscious Political Indoctrination Through Cultivating Subcultural'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J265" t="inlineStr"/>
@@ -45534,18 +45534,18 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Beatrise Ziedina</t>
+          <t>Dan Li</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -45566,7 +45566,7 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Tongue Tied'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Restoring Connections: The Role of Craft in Rebuilding Human-Object Relationships'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J266" t="inlineStr"/>
@@ -45574,18 +45574,18 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Yuxi Zhang</t>
+          <t>Xinyi Lou</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -45606,7 +45606,7 @@
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Invisible Wounds : Institutional Trauma and Self-Redemption Faced by Women with Unplanned Pregnancy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Navigating the Fluid Design Process: Embracing Uncertainty for Innovation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J267" t="inlineStr"/>
@@ -45614,18 +45614,18 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Pranav Abraham Varikad</t>
+          <t>Emma Brooke Schneider</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -45646,7 +45646,7 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'What Girls Want'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The Intersection of Collective and Visual Identities'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J268" t="inlineStr"/>
@@ -45654,18 +45654,18 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Koyna Mitra</t>
+          <t>Sining Sun</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -45686,7 +45686,7 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Identity Negotiation in Liminality : Migration, Gender, and Selfhood in Bollywood and Diasporic Cine'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Making a Better Future Will Come from Bringing Traditional Healing Practices into Technological Desi'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J269" t="inlineStr"/>
@@ -45694,18 +45694,18 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Keishla Marie Oquendo</t>
+          <t>Renjia Wang</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -45726,7 +45726,7 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Chrysalis'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Mapping the Correlations Between Design and Its Influences on Human Identity Via Technology'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J270" t="inlineStr"/>
@@ -45734,13 +45734,13 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Zhanlan Lei</t>
+          <t>Jonathan White</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -45766,7 +45766,7 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Films Enhance Animal Emotional Expression Beyond Reality'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The Future of Inconvenience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J271" t="inlineStr"/>
@@ -45774,13 +45774,13 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Nguyen Brian</t>
+          <t>Li Ye</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -45806,7 +45806,7 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'A Technical Overview of Selecting Lights while Dealing with Multiple Skin Tones'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Keep Our Individuality During the Information Overload'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J272" t="inlineStr"/>
@@ -45814,13 +45814,13 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Marina Kathy Saji</t>
+          <t>Muhammad Tayyab Younas</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -45846,7 +45846,7 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Impact of Interpretative Flashbacks on Narrative Complexity in Indian Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Unlearning Stereotypes: Visual Storytelling as Resistance to "Neocolonial Empire"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J273" t="inlineStr"/>
@@ -45854,13 +45854,13 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Fatima Diallo</t>
+          <t>Nora Brewington</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -45886,7 +45886,7 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Queer Film in Africa'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Adulterated Modernism: An Apathetic Approach to Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J274" t="inlineStr"/>
@@ -45894,13 +45894,13 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>C.J. Staidum</t>
+          <t>Jed Brysh</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45926,7 +45926,7 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Italian Neorealism : Where It Originated and The Connection It Has with Modern Day Documentary Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Harnessing the Hyperreal'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J275" t="inlineStr"/>
@@ -45934,13 +45934,13 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Noah Trainor</t>
+          <t>Xiangyi Chen</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45966,7 +45966,7 @@
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Subverting Cinematic Depictions of Toxic Masculinity in the Films of Noah Baumbach'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The McDonaldization of Daily Life'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J276" t="inlineStr"/>
@@ -45974,13 +45974,13 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>WeiChung Chen</t>
+          <t>Qiyue Guan</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -46006,7 +46006,7 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Designing and Executing Exterior Day for Night Scenes on a Micro-budget Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Past Memories, Present Simulations, Future Nostalgias'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J277" t="inlineStr"/>
@@ -46014,13 +46014,13 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Alec Dixon</t>
+          <t>Jingchuan Jin</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -46046,7 +46046,7 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Cutting to Glory : Editing Strategies in Sports Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Open Tent: Visual Identity System Supporting Autism Inclusion in Public Spaces'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J278" t="inlineStr"/>
@@ -46054,13 +46054,13 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Denise Francis Gordon</t>
+          <t>Yuxin Pan</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -46086,7 +46086,7 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Tyler Perry's Studios : A Modern Take on Vertical Integration'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The Pause That Holds Us: A Design for Midlife Transition'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J279" t="inlineStr"/>
@@ -46094,13 +46094,13 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Brennan Haley</t>
+          <t>Matthew Jackson Magill</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -46126,7 +46126,7 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Exposing the Repressed : The Horror of the Uncanny in Science Fiction Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'The Future We Deserve: Prioritizing Illusions Over Solutions'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J280" t="inlineStr"/>
@@ -46134,13 +46134,13 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Becca Robinson</t>
+          <t>Emilee Patterson</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46166,7 +46166,7 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'You Can't Joke About That : The Creation of Inheritance, a Short Film Inspired by a Study of the Psy'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Commercialism in Church'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J281" t="inlineStr"/>
@@ -46174,13 +46174,13 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Andrew James Taylor</t>
+          <t>Ronnie Riske</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46206,7 +46206,7 @@
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'The Art of the Spoof : One of Comedy's Most Challenging Acts to Accomplish in American Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Embodied Resistance: Fatness as a Queer Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J282" t="inlineStr"/>
@@ -46214,13 +46214,13 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Sarabi Woods</t>
+          <t>Varsha Sriram</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46246,7 +46246,7 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'The Push for Positive Media'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Cultural Threads: The Intersection of Graphic Design and Identity in Contemporary India'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J283" t="inlineStr"/>
@@ -46254,13 +46254,13 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Yuheng Zhang</t>
+          <t>Sichen Xin</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46286,7 +46286,7 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Duo'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Idealized Roles and Emotional Contrasts: The Impact of Women's Depictions in Romance Content on Girl'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J284" t="inlineStr"/>
@@ -46294,13 +46294,13 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Vusumuzi Mthembu</t>
+          <t>Jenne Dianne Pike Logsdon</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Graphic Design (SCAD)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46326,7 +46326,7 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Gaze : The Decolonizing of the Black, Queer Self'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Design; thesis title 'Boundless Faith: Cultivating the Storytelling of the Future of Faith'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J285" t="inlineStr"/>
@@ -46334,18 +46334,18 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Shakira Murphy</t>
+          <t>Keyu Fang</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -46366,7 +46366,7 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Fostered Deception'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Bridge: A Volunteer-Matching Platform for Intergenerational Connection'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J286" t="inlineStr"/>
@@ -46374,18 +46374,18 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Brandon Walker</t>
+          <t>Zhuokun Ma</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -46406,7 +46406,7 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Mindbound'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Home Companion Household Task Management System'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J287" t="inlineStr"/>
@@ -46414,18 +46414,18 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Chi Fan</t>
+          <t>Punasa Sihsobhon</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -46446,7 +46446,7 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Reimagining Intelligence : A Comparative Study of AI Representation in Contemporary Chinese and Amer'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Leveraging Technologies to Enhance the Pre-Travel Experience for Older Adults'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J288" t="inlineStr"/>
@@ -46454,18 +46454,18 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Stephen Ford</t>
+          <t>Alexandra Payne Bivins</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -46486,7 +46486,7 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Blood Upon Them'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Adaptive AI System for Personalized Education'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J289" t="inlineStr"/>
@@ -46494,13 +46494,13 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Annie Funderburk</t>
+          <t>Tian Xin</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -46526,7 +46526,7 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Death's A Drag'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Designing Trust: Enhancing New Drivers' Confidence in Semi-Autonomous Vehicles'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J290" t="inlineStr"/>
@@ -46534,13 +46534,13 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Xinzhu Liu</t>
+          <t>Yixian Wang</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>User Experience (UX) Design (SCAD)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -46566,7 +46566,7 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'How Nonlinear Narrative Editing Shapes Characters' Inner Worlds and Emotional Resonance within Visua'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: UI/UX Design; thesis title 'Rectifying Global Egg Control for Chinese Women with AIoT Through the Redesign of the Cryobank/Vial'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J291" t="inlineStr"/>
@@ -46574,18 +46574,18 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>R.J. Easy</t>
+          <t>Siri Lambu</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -46606,7 +46606,7 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Love Me!'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Nidde: The Aesthetics of Unease'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J292" t="inlineStr"/>
@@ -46614,18 +46614,18 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Zhaoning Lyu</t>
+          <t>Emily Macfarlane Chambers</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -46646,7 +46646,7 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Behind the Animal Act : The Making of Emotional Illusions in Pet Films'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Embodying Art : The Intersection of Art and Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J293" t="inlineStr"/>
@@ -46654,13 +46654,13 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Scott Joseph Moore</t>
+          <t>Yuqing Fu</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -46686,7 +46686,7 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Collective Consciousness and the Art of Film Making'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Nihil: You Don’t Exist, But Not Being Unseen: Mask Fetishism and Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J294" t="inlineStr"/>
@@ -46694,13 +46694,13 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Yili Ma</t>
+          <t>Fei Gao</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -46726,7 +46726,7 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Love Me!'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Ecstatic Rhythms: How Contemporary Fashion Design Draws Inspiration from the Animistic Beliefs of As'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J295" t="inlineStr"/>
@@ -46734,13 +46734,13 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Hanzhong Bai</t>
+          <t>Shuqi Guo</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -46766,7 +46766,7 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'A Time to Wither : The Convergence of Aging and Slow Cinema in Contemporary Film Practice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'An Afternoon with Wind: Exploring the Expression of Naturalness in Contemporary Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J296" t="inlineStr"/>
@@ -46774,13 +46774,13 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Cache Jill Capuyan</t>
+          <t>Thierry Kepgang Nana</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -46806,7 +46806,7 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'To Whom It May Concern : Illuminating Survivors of Male Domestic Violence and Exploring their Dismis'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Bami-America: Blending Bamiléké Textile Patterns from Grasslands with Western and African Fashion fo'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J297" t="inlineStr"/>
@@ -46814,13 +46814,13 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Shihao Fu</t>
+          <t>Chenjia Liu</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -46846,7 +46846,7 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Reincarnated Fear and the Unconscious : Symbolic Representations of Time and Identity in Cinema and'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Architectural Structures: Translating Gothic Cathedral into Contemporary Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J298" t="inlineStr"/>
@@ -46854,13 +46854,13 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Ziyou Li</t>
+          <t>Yunhan Meng</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -46886,7 +46886,7 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'How Cinematography Presents the Conflict between Gender Orientation and Family Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Fragments of the Self: Reconstructing Identity Through Deconstruction in Fashion Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J299" t="inlineStr"/>
@@ -46894,13 +46894,13 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Jiaxin Li</t>
+          <t>Sijia Pei</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -46926,7 +46926,7 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'The Artificial Identity : The Political Philosophy of Cyborg Bodies and Identity/Soul in Science Fic'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Exploring Zero-Waste Pattern Cutting Methods and Fabric Waste Reutilization to Achieve Zero-Waste De'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J300" t="inlineStr"/>
@@ -46934,13 +46934,13 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Eunique Foreman</t>
+          <t>Yiqing Wang</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -46966,7 +46966,7 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Sole Obsession'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Reviving Nuo Culture: Fashion as a Medium of Cultural Preservation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J301" t="inlineStr"/>
@@ -46974,13 +46974,13 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Esteban Larach</t>
+          <t>Wanxuan Jin</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -47006,7 +47006,7 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Moral Dilemmas in Thrillers : The Consequences of Split-Second Decisions'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Gaze Upon the Real Me: Identity Through the Rise of Jirai Kei and the Social Universality Behind'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J302" t="inlineStr"/>
@@ -47014,13 +47014,13 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Jacob McKee</t>
+          <t>Haoyue Zhao</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -47046,7 +47046,7 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'The Gay's Afoot : The Conceptualization and Making of 'My Dear Watson''; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Visual Resistance: Clothing, Power, and Punk Style in Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J303" t="inlineStr"/>
@@ -47054,13 +47054,13 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Garrison Rolle</t>
+          <t>Jon Fulton Adams</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -47086,7 +47086,7 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Colony'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Electric Fairy: The Queer Futurity of Derek Jarman'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J304" t="inlineStr"/>
@@ -47094,13 +47094,13 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Zitong Shu</t>
+          <t>Xiaoxiao Dong</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Film &amp; Television (SCAD)</t>
+          <t>Fashion (SCAD)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -47126,2698 +47126,18 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Medium: Filmmaking; thesis title 'Time Fragments : Exploring the Emotional Resonance of Nonlinear Narrative'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
+          <t>Medium: Fashion; thesis title 'Indeterminacy: The Evolution of Consciousness'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
         </is>
       </c>
       <c r="J305" t="inlineStr"/>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Damian James Standen</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Dogs &amp; Drunks : Representations of Canines and Alcoholics from the Silent Era to the Modern Day'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Ronesha Strickland</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Beneath The Surface'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Christopher Williams</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Beneath The Surface'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Haolan Liu</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr"/>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Captured Shadows : Self-Reflexivity and Masculine Duality in Neon-Noir'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Ivi D'vynne Wicks</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr"/>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'If You Got It : The Making of the Film'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Serenity M. Kelly</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr"/>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'NO! Progression'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Xinran Gu</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Love, Tears, and Choice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Alli Bargelski</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Kitty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Emily Carvalheiro</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Kitty'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Yulin Chen</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Love, Tears, and Choice'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Yeting Wang</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr"/>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Film &amp; Television (SCAD)</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>Medium: Filmmaking; thesis title 'Visual Storytelling Across Culture : Cinematography and Light in "Flight"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Caroline Constantin Fogg</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr"/>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Graphic Design in Nation Building, Nationalism, and Community'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Yuhan Feng</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Designing Silence: Rethinking Sexual Education in Contemporary China'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Jieun Kim</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Beyond Death: Digital Legacy, Mourning, and Posthumous Curation in the Digital Age'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Ruoxi Liu</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Redefining Success Narratives: How Visual Design Challenges Social Expectations'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Shivali Meenakshi Murali</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Beyond Vision'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Foster Whitney</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr"/>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The Luxury Commodification of Cannabis'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Mingxuan Duan</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Designing for Motivation: Transforming Procrastination with Graphic Design Strategies'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Yinxuan Duan</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr"/>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Raising Awareness Through Inclusive Graphic Design to Help Prevent Hearing Loss'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Junyuan Lan</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Veiled Resistance in the Age of Unconscious Political Indoctrination Through Cultivating Subcultural'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Dan Li</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Restoring Connections: The Role of Craft in Rebuilding Human-Object Relationships'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Xinyi Lou</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Navigating the Fluid Design Process: Embracing Uncertainty for Innovation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Emma Brooke Schneider</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr"/>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The Intersection of Collective and Visual Identities'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Sining Sun</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr"/>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Making a Better Future Will Come from Bringing Traditional Healing Practices into Technological Desi'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Renjia Wang</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr"/>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Mapping the Correlations Between Design and Its Influences on Human Identity Via Technology'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Jonathan White</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr"/>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The Future of Inconvenience'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Li Ye</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr"/>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Keep Our Individuality During the Information Overload'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Muhammad Tayyab Younas</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr"/>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Unlearning Stereotypes: Visual Storytelling as Resistance to "Neocolonial Empire"'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Nora Brewington</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr"/>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Adulterated Modernism: An Apathetic Approach to Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Jed Brysh</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr"/>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Harnessing the Hyperreal'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Xiangyi Chen</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr"/>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The McDonaldization of Daily Life'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Qiyue Guan</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Past Memories, Present Simulations, Future Nostalgias'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Jingchuan Jin</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr"/>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Open Tent: Visual Identity System Supporting Autism Inclusion in Public Spaces'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Trevor Kimathi Mugambi</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Enhancing African Representation in the Graphic Design Industry'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Yuxin Pan</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr"/>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The Pause That Holds Us: A Design for Midlife Transition'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Matthew Jackson Magill</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr"/>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'The Future We Deserve: Prioritizing Illusions Over Solutions'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Emilee Patterson</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr"/>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Commercialism in Church'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Ronnie Riske</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr"/>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Embodied Resistance: Fatness as a Queer Identity'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Caroline Schwarm</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr"/>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Mirror, Mirror on the Screen'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Xiaoyue Shen</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Visualizing Secondary Memory Through Graphic Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Varsha Sriram</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr"/>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Cultural Threads: The Intersection of Graphic Design and Identity in Contemporary India'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Sia Tyagi</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr"/>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Between Worlds: Redefining Design for Hybrid Realities'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Sichen Xin</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr"/>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Idealized Roles and Emotional Contrasts: The Impact of Women's Depictions in Romance Content on Girl'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Jenne Dianne Pike Logsdon</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Graphic Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>Medium: Design; thesis title 'Boundless Faith: Cultivating the Storytelling of the Future of Faith'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Keyu Fang</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr"/>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Bridge: A Volunteer-Matching Platform for Intergenerational Connection'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Zhuokun Ma</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr"/>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Home Companion Household Task Management System'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Punasa Sihsobhon</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr"/>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Leveraging Technologies to Enhance the Pre-Travel Experience for Older Adults'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Alexandra Payne Bivins</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Adaptive AI System for Personalized Education'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Tian Xin</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr"/>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Designing Trust: Enhancing New Drivers' Confidence in Semi-Autonomous Vehicles'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Yixian Wang</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr"/>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>User Experience (UX) Design (SCAD)</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t>Medium: UI/UX Design; thesis title 'Rectifying Global Egg Control for Chinese Women with AIoT Through the Redesign of the Cryobank/Vial'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Siri Lambu</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr"/>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Nidde: The Aesthetics of Unease'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Emily Macfarlane Chambers</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr"/>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Embodying Art : The Intersection of Art and Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Rupal Panwar</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr"/>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Creating Cultural Belonging Among Immigrants Through the Lens of Kashmir'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Yuqing Fu</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr"/>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Nihil: You Don’t Exist, But Not Being Unseen: Mask Fetishism and Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Fei Gao</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr"/>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Ecstatic Rhythms: How Contemporary Fashion Design Draws Inspiration from the Animistic Beliefs of As'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Shuqi Guo</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr"/>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr"/>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'An Afternoon with Wind: Exploring the Expression of Naturalness in Contemporary Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Jiani Hu</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr"/>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'In Between Black and White: The Fashion Potential of Yin-Yang Philosophy in the West'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J362" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Thierry Kepgang Nana</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr"/>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Bami-America: Blending Bamiléké Textile Patterns from Grasslands with Western and African Fashion fo'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J363" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Chenjia Liu</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr"/>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr"/>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Architectural Structures: Translating Gothic Cathedral into Contemporary Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J364" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Yunhan Meng</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr"/>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Fragments of the Self: Reconstructing Identity Through Deconstruction in Fashion Design'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Sijia Pei</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr"/>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Exploring Zero-Waste Pattern Cutting Methods and Fabric Waste Reutilization to Achieve Zero-Waste De'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Yiqing Wang</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Reviving Nuo Culture: Fashion as a Medium of Cultural Preservation'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J367" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Wanxuan Jin</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr"/>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Gaze Upon the Real Me: Identity Through the Rise of Jirai Kei and the Social Universality Behind'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J368" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Isaac Yu</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr"/>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Who Kills My Freedom'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J369" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Haoyue Zhao</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr"/>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Visual Resistance: Clothing, Power, and Punk Style in Fashion'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J370" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Jon Fulton Adams</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr"/>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Electric Fairy: The Queer Futurity of Derek Jarman'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J371" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Xiaoxiao Dong</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr"/>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Fashion (SCAD)</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>https://library.scad.edu/screens/theses.html</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>SCAD</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>Medium: Fashion; thesis title 'Indeterminacy: The Evolution of Consciousness'; from SCAD Thesis Digital Collection (library.scad.edu), no email/portfolio published on source page</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:J372"/>
+  <autoFilter ref="A5:J305"/>
   <dataValidations count="2">
-    <dataValidation sqref="G6:G372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:G305" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H6:H372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H305" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"No response,Interested,Not interested,Bounced,Follow-up needed"</formula1>
     </dataValidation>
   </dataValidations>
